--- a/context_DB/BFA_context_db.xlsx
+++ b/context_DB/BFA_context_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK352"/>
+  <dimension ref="A1:BL352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -686,60 +686,65 @@
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
+          <t>fatalities</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>event_count_evt3</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>ADM1_PCODE_evt3</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>event_type</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>sub_event_type</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>actor1</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>assoc_actor_1</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>actor2</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>assoc_actor_2</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>event_date</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
           <t>admin2</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>fatalities</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>event_count_evt3</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>event_type</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>sub_event_type</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>actor1</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>assoc_actor_1</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>actor2</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>assoc_actor_2</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>event_date</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>ratio IDP/ToTN - HPC2025</t>
         </is>
@@ -846,8 +851,9 @@
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="n">
-        <v>0</v>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="n">
+        <v>0.08970824718584884</v>
       </c>
     </row>
     <row r="3">
@@ -951,8 +957,9 @@
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr"/>
       <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="n">
-        <v>0</v>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="n">
+        <v>0.01109334725439655</v>
       </c>
     </row>
     <row r="4">
@@ -1056,8 +1063,9 @@
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr"/>
       <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="n">
-        <v>0</v>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="n">
+        <v>0.03553784198945489</v>
       </c>
     </row>
     <row r="5">
@@ -1154,16 +1162,16 @@
           <t>Centre</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>Kadiogo</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
         <v>1</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>BF13</t>
+        </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
@@ -1194,11 +1202,16 @@
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>30 April 2025</t>
-        </is>
-      </c>
-      <c r="BK5" t="n">
-        <v>0</v>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>Kadiogo</t>
+        </is>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.01268001551036748</v>
       </c>
     </row>
     <row r="6">
@@ -1302,8 +1315,9 @@
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr"/>
       <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="n">
-        <v>0</v>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="n">
+        <v>0.2394418604651163</v>
       </c>
     </row>
     <row r="7">
@@ -1407,8 +1421,9 @@
       <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr"/>
       <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="n">
-        <v>0</v>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="n">
+        <v>0.008702691762801052</v>
       </c>
     </row>
     <row r="8">
@@ -1512,8 +1527,9 @@
       <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr"/>
       <c r="BJ8" t="inlineStr"/>
-      <c r="BK8" t="n">
-        <v>0</v>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="n">
+        <v>0.04045832866793565</v>
       </c>
     </row>
     <row r="9">
@@ -1617,8 +1633,9 @@
       <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="inlineStr"/>
       <c r="BJ9" t="inlineStr"/>
-      <c r="BK9" t="n">
-        <v>0</v>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="n">
+        <v>0.01919215778906342</v>
       </c>
     </row>
     <row r="10">
@@ -1722,7 +1739,8 @@
       <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="inlineStr"/>
       <c r="BJ10" t="inlineStr"/>
-      <c r="BK10" t="n">
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1827,8 +1845,9 @@
       <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr"/>
       <c r="BJ11" t="inlineStr"/>
-      <c r="BK11" t="n">
-        <v>0</v>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="n">
+        <v>0.2306870996106017</v>
       </c>
     </row>
     <row r="12">
@@ -1932,8 +1951,9 @@
       <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr"/>
       <c r="BJ12" t="inlineStr"/>
-      <c r="BK12" t="n">
-        <v>0</v>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="n">
+        <v>0.01064844246662429</v>
       </c>
     </row>
     <row r="13">
@@ -2037,8 +2057,9 @@
       <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr"/>
       <c r="BJ13" t="inlineStr"/>
-      <c r="BK13" t="n">
-        <v>0</v>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="n">
+        <v>0.002213307511412367</v>
       </c>
     </row>
     <row r="14">
@@ -2142,8 +2163,9 @@
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr"/>
       <c r="BJ14" t="inlineStr"/>
-      <c r="BK14" t="n">
-        <v>0</v>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="n">
+        <v>0.003407766119630526</v>
       </c>
     </row>
     <row r="15">
@@ -2247,7 +2269,8 @@
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr"/>
       <c r="BJ15" t="inlineStr"/>
-      <c r="BK15" t="n">
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2352,8 +2375,9 @@
       <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr"/>
       <c r="BJ16" t="inlineStr"/>
-      <c r="BK16" t="n">
-        <v>0</v>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="n">
+        <v>0.4164739141608841</v>
       </c>
     </row>
     <row r="17">
@@ -2457,8 +2481,9 @@
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr"/>
       <c r="BJ17" t="inlineStr"/>
-      <c r="BK17" t="n">
-        <v>0</v>
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="n">
+        <v>0.3568124752213559</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2587,8 @@
       <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr"/>
       <c r="BJ18" t="inlineStr"/>
-      <c r="BK18" t="n">
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2667,8 +2693,9 @@
       <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr"/>
       <c r="BJ19" t="inlineStr"/>
-      <c r="BK19" t="n">
-        <v>0</v>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="n">
+        <v>0.1777642647207865</v>
       </c>
     </row>
     <row r="20">
@@ -2772,8 +2799,9 @@
       <c r="BH20" t="inlineStr"/>
       <c r="BI20" t="inlineStr"/>
       <c r="BJ20" t="inlineStr"/>
-      <c r="BK20" t="n">
-        <v>0</v>
+      <c r="BK20" t="inlineStr"/>
+      <c r="BL20" t="n">
+        <v>0.09021458644574222</v>
       </c>
     </row>
     <row r="21">
@@ -2877,7 +2905,8 @@
       <c r="BH21" t="inlineStr"/>
       <c r="BI21" t="inlineStr"/>
       <c r="BJ21" t="inlineStr"/>
-      <c r="BK21" t="n">
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2982,8 +3011,9 @@
       <c r="BH22" t="inlineStr"/>
       <c r="BI22" t="inlineStr"/>
       <c r="BJ22" t="inlineStr"/>
-      <c r="BK22" t="n">
-        <v>0</v>
+      <c r="BK22" t="inlineStr"/>
+      <c r="BL22" t="n">
+        <v>0.03078563337109349</v>
       </c>
     </row>
     <row r="23">
@@ -3087,8 +3117,9 @@
       <c r="BH23" t="inlineStr"/>
       <c r="BI23" t="inlineStr"/>
       <c r="BJ23" t="inlineStr"/>
-      <c r="BK23" t="n">
-        <v>0</v>
+      <c r="BK23" t="inlineStr"/>
+      <c r="BL23" t="n">
+        <v>0.06987838367987446</v>
       </c>
     </row>
     <row r="24">
@@ -3192,8 +3223,9 @@
       <c r="BH24" t="inlineStr"/>
       <c r="BI24" t="inlineStr"/>
       <c r="BJ24" t="inlineStr"/>
-      <c r="BK24" t="n">
-        <v>0</v>
+      <c r="BK24" t="inlineStr"/>
+      <c r="BL24" t="n">
+        <v>0.005443832458050467</v>
       </c>
     </row>
     <row r="25">
@@ -3297,8 +3329,9 @@
       <c r="BH25" t="inlineStr"/>
       <c r="BI25" t="inlineStr"/>
       <c r="BJ25" t="inlineStr"/>
-      <c r="BK25" t="n">
-        <v>0</v>
+      <c r="BK25" t="inlineStr"/>
+      <c r="BL25" t="n">
+        <v>0.2011278195488722</v>
       </c>
     </row>
     <row r="26">
@@ -3402,8 +3435,9 @@
       <c r="BH26" t="inlineStr"/>
       <c r="BI26" t="inlineStr"/>
       <c r="BJ26" t="inlineStr"/>
-      <c r="BK26" t="n">
-        <v>0</v>
+      <c r="BK26" t="inlineStr"/>
+      <c r="BL26" t="n">
+        <v>0.5494021397105098</v>
       </c>
     </row>
     <row r="27">
@@ -3562,16 +3596,16 @@
           <t>Boucle du Mouhoun</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>Kossi</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>7</v>
       </c>
       <c r="BA27" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB27" t="n">
         <v>1</v>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>BF46</t>
+        </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
@@ -3602,11 +3636,16 @@
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>22 May 2024</t>
-        </is>
-      </c>
-      <c r="BK27" t="n">
-        <v>0</v>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="BK27" t="inlineStr">
+        <is>
+          <t>Kossi</t>
+        </is>
+      </c>
+      <c r="BL27" t="n">
+        <v>0.01032702237521515</v>
       </c>
     </row>
     <row r="28">
@@ -3710,8 +3749,9 @@
       <c r="BH28" t="inlineStr"/>
       <c r="BI28" t="inlineStr"/>
       <c r="BJ28" t="inlineStr"/>
-      <c r="BK28" t="n">
-        <v>0</v>
+      <c r="BK28" t="inlineStr"/>
+      <c r="BL28" t="n">
+        <v>0.2239299223571571</v>
       </c>
     </row>
     <row r="29">
@@ -3815,8 +3855,9 @@
       <c r="BH29" t="inlineStr"/>
       <c r="BI29" t="inlineStr"/>
       <c r="BJ29" t="inlineStr"/>
-      <c r="BK29" t="n">
-        <v>0</v>
+      <c r="BK29" t="inlineStr"/>
+      <c r="BL29" t="n">
+        <v>0.002007909948281107</v>
       </c>
     </row>
     <row r="30">
@@ -3920,8 +3961,9 @@
       <c r="BH30" t="inlineStr"/>
       <c r="BI30" t="inlineStr"/>
       <c r="BJ30" t="inlineStr"/>
-      <c r="BK30" t="n">
-        <v>0</v>
+      <c r="BK30" t="inlineStr"/>
+      <c r="BL30" t="n">
+        <v>0.1343407006465193</v>
       </c>
     </row>
     <row r="31">
@@ -4025,8 +4067,9 @@
       <c r="BH31" t="inlineStr"/>
       <c r="BI31" t="inlineStr"/>
       <c r="BJ31" t="inlineStr"/>
-      <c r="BK31" t="n">
-        <v>0</v>
+      <c r="BK31" t="inlineStr"/>
+      <c r="BL31" t="n">
+        <v>0.04295259306395164</v>
       </c>
     </row>
     <row r="32">
@@ -4130,8 +4173,9 @@
       <c r="BH32" t="inlineStr"/>
       <c r="BI32" t="inlineStr"/>
       <c r="BJ32" t="inlineStr"/>
-      <c r="BK32" t="n">
-        <v>0</v>
+      <c r="BK32" t="inlineStr"/>
+      <c r="BL32" t="n">
+        <v>0.08595702148925537</v>
       </c>
     </row>
     <row r="33">
@@ -4228,30 +4272,30 @@
           <t>Boucle du Mouhoun</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>Kossi</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>1</v>
       </c>
       <c r="BA33" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB33" t="n">
         <v>2</v>
       </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>BF46</t>
+        </is>
+      </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>Violence against civilians ---- Explosions/Remote violence</t>
+          <t>Explosions/Remote violence ---- Violence against civilians</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>Attack ---- Shelling/artillery/missile attack</t>
+          <t>Shelling/artillery/missile attack ---- Attack</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
-          <t>Unidentified Armed Group (Burkina Faso) ---- JNIM: Group for Support of Islam and Muslims</t>
+          <t>JNIM: Group for Support of Islam and Muslims ---- Unidentified Armed Group (Burkina Faso)</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr"/>
@@ -4267,16 +4311,21 @@
       </c>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>On 19 May 2024, unidentified gunmen killed a student on the outskirts of the town of Nouna (Nouna, Kossi). ---- On 27 February 2024, JNIM militants fired mortar shells at the town of Nouna (Nouna, Kossi). The shells fell in a franco-Arab school and did not explode.</t>
+          <t>On 27 February 2024, JNIM militants fired mortar shells at the town of Nouna (Nouna, Kossi). The shells fell in a franco-Arab school and did not explode. ---- On 19 May 2024, unidentified gunmen killed a student on the outskirts of the town of Nouna (Nouna, Kossi).</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr">
         <is>
-          <t>19 May 2024 ---- 27 February 2024</t>
-        </is>
-      </c>
-      <c r="BK33" t="n">
-        <v>0</v>
+          <t>2024-02-27 ---- 2024-05-19</t>
+        </is>
+      </c>
+      <c r="BK33" t="inlineStr">
+        <is>
+          <t>Kossi</t>
+        </is>
+      </c>
+      <c r="BL33" t="n">
+        <v>0.5339677727247206</v>
       </c>
     </row>
     <row r="34">
@@ -4380,8 +4429,9 @@
       <c r="BH34" t="inlineStr"/>
       <c r="BI34" t="inlineStr"/>
       <c r="BJ34" t="inlineStr"/>
-      <c r="BK34" t="n">
-        <v>0</v>
+      <c r="BK34" t="inlineStr"/>
+      <c r="BL34" t="n">
+        <v>0.2647921760391198</v>
       </c>
     </row>
     <row r="35">
@@ -4478,16 +4528,16 @@
           <t>Boucle du Mouhoun</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>Mouhoun</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB35" t="n">
         <v>1</v>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>BF46</t>
+        </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
@@ -4514,11 +4564,16 @@
       </c>
       <c r="BJ35" t="inlineStr">
         <is>
-          <t>17 January 2025</t>
-        </is>
-      </c>
-      <c r="BK35" t="n">
-        <v>0</v>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="BK35" t="inlineStr">
+        <is>
+          <t>Mouhoun</t>
+        </is>
+      </c>
+      <c r="BL35" t="n">
+        <v>0.01289415545290219</v>
       </c>
     </row>
     <row r="36">
@@ -4615,30 +4670,30 @@
           <t>Boucle du Mouhoun</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>Mouhoun</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB36" t="n">
         <v>2</v>
       </c>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>BF46</t>
+        </is>
+      </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>Riots ---- Protests</t>
+          <t>Protests ---- Riots</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>Violent demonstration ---- Protest with intervention</t>
+          <t>Protest with intervention ---- Violent demonstration</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>Rioters (Burkina Faso) ---- Protesters (Burkina Faso)</t>
+          <t>Protesters (Burkina Faso) ---- Rioters (Burkina Faso)</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
@@ -4654,16 +4709,21 @@
       <c r="BH36" t="inlineStr"/>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>On 4 October 2024, students from the modern literature faculty, gathered and demonstrated at the public university 'Daniel Ouezin COULIBALY' in Dedougou (Dedougou, Mouhoun) to claim the scheduling of catch-up sessions. The demonstration turned violent and caused material damage. The police intervened in shooting tear gas against students. A number of students were injured. ---- On 1 August 2024, students protested against making up classes during the vacations at the 'Daniel Ouezzin Coulibaly' university in Dedougou (Dedougou, Mouhoun). The police intervened and fired tear gas to disperse the protesters.</t>
+          <t>On 1 August 2024, students protested against making up classes during the vacations at the 'Daniel Ouezzin Coulibaly' university in Dedougou (Dedougou, Mouhoun). The police intervened and fired tear gas to disperse the protesters. ---- On 4 October 2024, students from the modern literature faculty, gathered and demonstrated at the public university 'Daniel Ouezin COULIBALY' in Dedougou (Dedougou, Mouhoun) to claim the scheduling of catch-up sessions. The demonstration turned violent and caused material damage. The police intervened in shooting tear gas against students. A number of students were injured.</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr">
         <is>
-          <t>04 October 2024 ---- 01 August 2024</t>
-        </is>
-      </c>
-      <c r="BK36" t="n">
-        <v>0</v>
+          <t>2024-08-01 ---- 2024-10-04</t>
+        </is>
+      </c>
+      <c r="BK36" t="inlineStr">
+        <is>
+          <t>Mouhoun</t>
+        </is>
+      </c>
+      <c r="BL36" t="n">
+        <v>0.1740707701457032</v>
       </c>
     </row>
     <row r="37">
@@ -4767,8 +4827,9 @@
       <c r="BH37" t="inlineStr"/>
       <c r="BI37" t="inlineStr"/>
       <c r="BJ37" t="inlineStr"/>
-      <c r="BK37" t="n">
-        <v>0</v>
+      <c r="BK37" t="inlineStr"/>
+      <c r="BL37" t="n">
+        <v>0.09301075268817205</v>
       </c>
     </row>
     <row r="38">
@@ -4872,8 +4933,9 @@
       <c r="BH38" t="inlineStr"/>
       <c r="BI38" t="inlineStr"/>
       <c r="BJ38" t="inlineStr"/>
-      <c r="BK38" t="n">
-        <v>0</v>
+      <c r="BK38" t="inlineStr"/>
+      <c r="BL38" t="n">
+        <v>0.01221608904171568</v>
       </c>
     </row>
     <row r="39">
@@ -4977,8 +5039,9 @@
       <c r="BH39" t="inlineStr"/>
       <c r="BI39" t="inlineStr"/>
       <c r="BJ39" t="inlineStr"/>
-      <c r="BK39" t="n">
-        <v>0</v>
+      <c r="BK39" t="inlineStr"/>
+      <c r="BL39" t="n">
+        <v>0.004810140908833682</v>
       </c>
     </row>
     <row r="40">
@@ -5082,8 +5145,9 @@
       <c r="BH40" t="inlineStr"/>
       <c r="BI40" t="inlineStr"/>
       <c r="BJ40" t="inlineStr"/>
-      <c r="BK40" t="n">
-        <v>0</v>
+      <c r="BK40" t="inlineStr"/>
+      <c r="BL40" t="n">
+        <v>0.002365772484863066</v>
       </c>
     </row>
     <row r="41">
@@ -5187,8 +5251,9 @@
       <c r="BH41" t="inlineStr"/>
       <c r="BI41" t="inlineStr"/>
       <c r="BJ41" t="inlineStr"/>
-      <c r="BK41" t="n">
-        <v>0</v>
+      <c r="BK41" t="inlineStr"/>
+      <c r="BL41" t="n">
+        <v>0.04532191265060241</v>
       </c>
     </row>
     <row r="42">
@@ -5292,8 +5357,9 @@
       <c r="BH42" t="inlineStr"/>
       <c r="BI42" t="inlineStr"/>
       <c r="BJ42" t="inlineStr"/>
-      <c r="BK42" t="n">
-        <v>0</v>
+      <c r="BK42" t="inlineStr"/>
+      <c r="BL42" t="n">
+        <v>0.00368689733408962</v>
       </c>
     </row>
     <row r="43">
@@ -5397,8 +5463,9 @@
       <c r="BH43" t="inlineStr"/>
       <c r="BI43" t="inlineStr"/>
       <c r="BJ43" t="inlineStr"/>
-      <c r="BK43" t="n">
-        <v>0</v>
+      <c r="BK43" t="inlineStr"/>
+      <c r="BL43" t="n">
+        <v>0.0002828054298642534</v>
       </c>
     </row>
     <row r="44">
@@ -5502,8 +5569,9 @@
       <c r="BH44" t="inlineStr"/>
       <c r="BI44" t="inlineStr"/>
       <c r="BJ44" t="inlineStr"/>
-      <c r="BK44" t="n">
-        <v>0</v>
+      <c r="BK44" t="inlineStr"/>
+      <c r="BL44" t="n">
+        <v>0.007404914170313026</v>
       </c>
     </row>
     <row r="45">
@@ -5607,8 +5675,9 @@
       <c r="BH45" t="inlineStr"/>
       <c r="BI45" t="inlineStr"/>
       <c r="BJ45" t="inlineStr"/>
-      <c r="BK45" t="n">
-        <v>0</v>
+      <c r="BK45" t="inlineStr"/>
+      <c r="BL45" t="n">
+        <v>0.3866658224642269</v>
       </c>
     </row>
     <row r="46">
@@ -5712,8 +5781,9 @@
       <c r="BH46" t="inlineStr"/>
       <c r="BI46" t="inlineStr"/>
       <c r="BJ46" t="inlineStr"/>
-      <c r="BK46" t="n">
-        <v>0</v>
+      <c r="BK46" t="inlineStr"/>
+      <c r="BL46" t="n">
+        <v>0.01426317067249332</v>
       </c>
     </row>
     <row r="47">
@@ -5817,8 +5887,9 @@
       <c r="BH47" t="inlineStr"/>
       <c r="BI47" t="inlineStr"/>
       <c r="BJ47" t="inlineStr"/>
-      <c r="BK47" t="n">
-        <v>0</v>
+      <c r="BK47" t="inlineStr"/>
+      <c r="BL47" t="n">
+        <v>0.5267874826698357</v>
       </c>
     </row>
     <row r="48">
@@ -5922,8 +5993,9 @@
       <c r="BH48" t="inlineStr"/>
       <c r="BI48" t="inlineStr"/>
       <c r="BJ48" t="inlineStr"/>
-      <c r="BK48" t="n">
-        <v>0</v>
+      <c r="BK48" t="inlineStr"/>
+      <c r="BL48" t="n">
+        <v>0.04740421080162155</v>
       </c>
     </row>
     <row r="49">
@@ -6015,19 +6087,64 @@
       <c r="AV49" t="inlineStr"/>
       <c r="AW49" t="inlineStr"/>
       <c r="AX49" t="inlineStr"/>
-      <c r="AY49" t="inlineStr"/>
-      <c r="AZ49" t="inlineStr"/>
-      <c r="BA49" t="inlineStr"/>
-      <c r="BB49" t="inlineStr"/>
-      <c r="BC49" t="inlineStr"/>
-      <c r="BD49" t="inlineStr"/>
-      <c r="BE49" t="inlineStr"/>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Boucle du Mouhoun</t>
+        </is>
+      </c>
+      <c r="AZ49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>BF46</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="BE49" t="inlineStr">
+        <is>
+          <t>JNIM: Group for Support of Islam and Muslims</t>
+        </is>
+      </c>
       <c r="BF49" t="inlineStr"/>
-      <c r="BG49" t="inlineStr"/>
-      <c r="BH49" t="inlineStr"/>
-      <c r="BI49" t="inlineStr"/>
-      <c r="BJ49" t="inlineStr"/>
-      <c r="BK49" t="n">
+      <c r="BG49" t="inlineStr">
+        <is>
+          <t>Civilians (Burkina Faso)</t>
+        </is>
+      </c>
+      <c r="BH49" t="inlineStr">
+        <is>
+          <t>Teachers (Burkina Faso)</t>
+        </is>
+      </c>
+      <c r="BI49" t="inlineStr">
+        <is>
+          <t>On 1 August 2025, an armed group (likely JNIM militants, based on location) killed a teacher on the outskirts of Gomboro (Gomboro, Sourou).</t>
+        </is>
+      </c>
+      <c r="BJ49" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="BK49" t="inlineStr">
+        <is>
+          <t>Sourou</t>
+        </is>
+      </c>
+      <c r="BL49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6132,7 +6249,8 @@
       <c r="BH50" t="inlineStr"/>
       <c r="BI50" t="inlineStr"/>
       <c r="BJ50" t="inlineStr"/>
-      <c r="BK50" t="n">
+      <c r="BK50" t="inlineStr"/>
+      <c r="BL50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6237,8 +6355,9 @@
       <c r="BH51" t="inlineStr"/>
       <c r="BI51" t="inlineStr"/>
       <c r="BJ51" t="inlineStr"/>
-      <c r="BK51" t="n">
-        <v>0</v>
+      <c r="BK51" t="inlineStr"/>
+      <c r="BL51" t="n">
+        <v>0.3749603602460836</v>
       </c>
     </row>
     <row r="52">
@@ -6342,8 +6461,9 @@
       <c r="BH52" t="inlineStr"/>
       <c r="BI52" t="inlineStr"/>
       <c r="BJ52" t="inlineStr"/>
-      <c r="BK52" t="n">
-        <v>0</v>
+      <c r="BK52" t="inlineStr"/>
+      <c r="BL52" t="n">
+        <v>0.004392386530014641</v>
       </c>
     </row>
     <row r="53">
@@ -6447,8 +6567,9 @@
       <c r="BH53" t="inlineStr"/>
       <c r="BI53" t="inlineStr"/>
       <c r="BJ53" t="inlineStr"/>
-      <c r="BK53" t="n">
-        <v>0</v>
+      <c r="BK53" t="inlineStr"/>
+      <c r="BL53" t="n">
+        <v>0.004162447969400383</v>
       </c>
     </row>
     <row r="54">
@@ -6552,7 +6673,8 @@
       <c r="BH54" t="inlineStr"/>
       <c r="BI54" t="inlineStr"/>
       <c r="BJ54" t="inlineStr"/>
-      <c r="BK54" t="n">
+      <c r="BK54" t="inlineStr"/>
+      <c r="BL54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6657,8 +6779,9 @@
       <c r="BH55" t="inlineStr"/>
       <c r="BI55" t="inlineStr"/>
       <c r="BJ55" t="inlineStr"/>
-      <c r="BK55" t="n">
-        <v>0</v>
+      <c r="BK55" t="inlineStr"/>
+      <c r="BL55" t="n">
+        <v>0.3722345912126934</v>
       </c>
     </row>
     <row r="56">
@@ -6762,8 +6885,9 @@
       <c r="BH56" t="inlineStr"/>
       <c r="BI56" t="inlineStr"/>
       <c r="BJ56" t="inlineStr"/>
-      <c r="BK56" t="n">
-        <v>0</v>
+      <c r="BK56" t="inlineStr"/>
+      <c r="BL56" t="n">
+        <v>0.02738190306529885</v>
       </c>
     </row>
     <row r="57">
@@ -6867,8 +6991,9 @@
       <c r="BH57" t="inlineStr"/>
       <c r="BI57" t="inlineStr"/>
       <c r="BJ57" t="inlineStr"/>
-      <c r="BK57" t="n">
-        <v>0</v>
+      <c r="BK57" t="inlineStr"/>
+      <c r="BL57" t="n">
+        <v>0.02949061662198391</v>
       </c>
     </row>
     <row r="58">
@@ -6972,8 +7097,9 @@
       <c r="BH58" t="inlineStr"/>
       <c r="BI58" t="inlineStr"/>
       <c r="BJ58" t="inlineStr"/>
-      <c r="BK58" t="n">
-        <v>0</v>
+      <c r="BK58" t="inlineStr"/>
+      <c r="BL58" t="n">
+        <v>0.0803577869148092</v>
       </c>
     </row>
     <row r="59">
@@ -7077,8 +7203,9 @@
       <c r="BH59" t="inlineStr"/>
       <c r="BI59" t="inlineStr"/>
       <c r="BJ59" t="inlineStr"/>
-      <c r="BK59" t="n">
-        <v>0</v>
+      <c r="BK59" t="inlineStr"/>
+      <c r="BL59" t="n">
+        <v>0.002921942395992765</v>
       </c>
     </row>
     <row r="60">
@@ -7182,8 +7309,9 @@
       <c r="BH60" t="inlineStr"/>
       <c r="BI60" t="inlineStr"/>
       <c r="BJ60" t="inlineStr"/>
-      <c r="BK60" t="n">
-        <v>0</v>
+      <c r="BK60" t="inlineStr"/>
+      <c r="BL60" t="n">
+        <v>0.1326126911934208</v>
       </c>
     </row>
     <row r="61">
@@ -7287,8 +7415,9 @@
       <c r="BH61" t="inlineStr"/>
       <c r="BI61" t="inlineStr"/>
       <c r="BJ61" t="inlineStr"/>
-      <c r="BK61" t="n">
-        <v>0</v>
+      <c r="BK61" t="inlineStr"/>
+      <c r="BL61" t="n">
+        <v>0.01649703342819931</v>
       </c>
     </row>
     <row r="62">
@@ -7392,8 +7521,9 @@
       <c r="BH62" t="inlineStr"/>
       <c r="BI62" t="inlineStr"/>
       <c r="BJ62" t="inlineStr"/>
-      <c r="BK62" t="n">
-        <v>0</v>
+      <c r="BK62" t="inlineStr"/>
+      <c r="BL62" t="n">
+        <v>0.1421098517872711</v>
       </c>
     </row>
     <row r="63">
@@ -7497,8 +7627,9 @@
       <c r="BH63" t="inlineStr"/>
       <c r="BI63" t="inlineStr"/>
       <c r="BJ63" t="inlineStr"/>
-      <c r="BK63" t="n">
-        <v>0</v>
+      <c r="BK63" t="inlineStr"/>
+      <c r="BL63" t="n">
+        <v>0.002541213266436437</v>
       </c>
     </row>
     <row r="64">
@@ -7602,8 +7733,9 @@
       <c r="BH64" t="inlineStr"/>
       <c r="BI64" t="inlineStr"/>
       <c r="BJ64" t="inlineStr"/>
-      <c r="BK64" t="n">
-        <v>0</v>
+      <c r="BK64" t="inlineStr"/>
+      <c r="BL64" t="n">
+        <v>0.02642193802570276</v>
       </c>
     </row>
     <row r="65">
@@ -7707,7 +7839,8 @@
       <c r="BH65" t="inlineStr"/>
       <c r="BI65" t="inlineStr"/>
       <c r="BJ65" t="inlineStr"/>
-      <c r="BK65" t="n">
+      <c r="BK65" t="inlineStr"/>
+      <c r="BL65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7812,7 +7945,8 @@
       <c r="BH66" t="inlineStr"/>
       <c r="BI66" t="inlineStr"/>
       <c r="BJ66" t="inlineStr"/>
-      <c r="BK66" t="n">
+      <c r="BK66" t="inlineStr"/>
+      <c r="BL66" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7917,7 +8051,8 @@
       <c r="BH67" t="inlineStr"/>
       <c r="BI67" t="inlineStr"/>
       <c r="BJ67" t="inlineStr"/>
-      <c r="BK67" t="n">
+      <c r="BK67" t="inlineStr"/>
+      <c r="BL67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8022,7 +8157,8 @@
       <c r="BH68" t="inlineStr"/>
       <c r="BI68" t="inlineStr"/>
       <c r="BJ68" t="inlineStr"/>
-      <c r="BK68" t="n">
+      <c r="BK68" t="inlineStr"/>
+      <c r="BL68" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8127,7 +8263,8 @@
       <c r="BH69" t="inlineStr"/>
       <c r="BI69" t="inlineStr"/>
       <c r="BJ69" t="inlineStr"/>
-      <c r="BK69" t="n">
+      <c r="BK69" t="inlineStr"/>
+      <c r="BL69" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8232,7 +8369,8 @@
       <c r="BH70" t="inlineStr"/>
       <c r="BI70" t="inlineStr"/>
       <c r="BJ70" t="inlineStr"/>
-      <c r="BK70" t="n">
+      <c r="BK70" t="inlineStr"/>
+      <c r="BL70" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8337,7 +8475,8 @@
       <c r="BH71" t="inlineStr"/>
       <c r="BI71" t="inlineStr"/>
       <c r="BJ71" t="inlineStr"/>
-      <c r="BK71" t="n">
+      <c r="BK71" t="inlineStr"/>
+      <c r="BL71" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8442,7 +8581,8 @@
       <c r="BH72" t="inlineStr"/>
       <c r="BI72" t="inlineStr"/>
       <c r="BJ72" t="inlineStr"/>
-      <c r="BK72" t="n">
+      <c r="BK72" t="inlineStr"/>
+      <c r="BL72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8547,8 +8687,9 @@
       <c r="BH73" t="inlineStr"/>
       <c r="BI73" t="inlineStr"/>
       <c r="BJ73" t="inlineStr"/>
-      <c r="BK73" t="n">
-        <v>0</v>
+      <c r="BK73" t="inlineStr"/>
+      <c r="BL73" t="n">
+        <v>0.02097589051608365</v>
       </c>
     </row>
     <row r="74">
@@ -8652,8 +8793,9 @@
       <c r="BH74" t="inlineStr"/>
       <c r="BI74" t="inlineStr"/>
       <c r="BJ74" t="inlineStr"/>
-      <c r="BK74" t="n">
-        <v>0</v>
+      <c r="BK74" t="inlineStr"/>
+      <c r="BL74" t="n">
+        <v>0.01776023680315738</v>
       </c>
     </row>
     <row r="75">
@@ -8757,8 +8899,9 @@
       <c r="BH75" t="inlineStr"/>
       <c r="BI75" t="inlineStr"/>
       <c r="BJ75" t="inlineStr"/>
-      <c r="BK75" t="n">
-        <v>0</v>
+      <c r="BK75" t="inlineStr"/>
+      <c r="BL75" t="n">
+        <v>0.001736111111111111</v>
       </c>
     </row>
     <row r="76">
@@ -8862,8 +9005,9 @@
       <c r="BH76" t="inlineStr"/>
       <c r="BI76" t="inlineStr"/>
       <c r="BJ76" t="inlineStr"/>
-      <c r="BK76" t="n">
-        <v>0</v>
+      <c r="BK76" t="inlineStr"/>
+      <c r="BL76" t="n">
+        <v>0.001862032275226104</v>
       </c>
     </row>
     <row r="77">
@@ -8967,8 +9111,9 @@
       <c r="BH77" t="inlineStr"/>
       <c r="BI77" t="inlineStr"/>
       <c r="BJ77" t="inlineStr"/>
-      <c r="BK77" t="n">
-        <v>0</v>
+      <c r="BK77" t="inlineStr"/>
+      <c r="BL77" t="n">
+        <v>0.03881511746680286</v>
       </c>
     </row>
     <row r="78">
@@ -9072,7 +9217,8 @@
       <c r="BH78" t="inlineStr"/>
       <c r="BI78" t="inlineStr"/>
       <c r="BJ78" t="inlineStr"/>
-      <c r="BK78" t="n">
+      <c r="BK78" t="inlineStr"/>
+      <c r="BL78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9177,8 +9323,9 @@
       <c r="BH79" t="inlineStr"/>
       <c r="BI79" t="inlineStr"/>
       <c r="BJ79" t="inlineStr"/>
-      <c r="BK79" t="n">
-        <v>0</v>
+      <c r="BK79" t="inlineStr"/>
+      <c r="BL79" t="n">
+        <v>0.002449361514751211</v>
       </c>
     </row>
     <row r="80">
@@ -9282,8 +9429,9 @@
       <c r="BH80" t="inlineStr"/>
       <c r="BI80" t="inlineStr"/>
       <c r="BJ80" t="inlineStr"/>
-      <c r="BK80" t="n">
-        <v>0</v>
+      <c r="BK80" t="inlineStr"/>
+      <c r="BL80" t="n">
+        <v>0.003265602322206096</v>
       </c>
     </row>
     <row r="81">
@@ -9387,8 +9535,9 @@
       <c r="BH81" t="inlineStr"/>
       <c r="BI81" t="inlineStr"/>
       <c r="BJ81" t="inlineStr"/>
-      <c r="BK81" t="n">
-        <v>0</v>
+      <c r="BK81" t="inlineStr"/>
+      <c r="BL81" t="n">
+        <v>0.007485175464178088</v>
       </c>
     </row>
     <row r="82">
@@ -9492,8 +9641,9 @@
       <c r="BH82" t="inlineStr"/>
       <c r="BI82" t="inlineStr"/>
       <c r="BJ82" t="inlineStr"/>
-      <c r="BK82" t="n">
-        <v>0</v>
+      <c r="BK82" t="inlineStr"/>
+      <c r="BL82" t="n">
+        <v>0.00359009888517982</v>
       </c>
     </row>
     <row r="83">
@@ -9597,8 +9747,9 @@
       <c r="BH83" t="inlineStr"/>
       <c r="BI83" t="inlineStr"/>
       <c r="BJ83" t="inlineStr"/>
-      <c r="BK83" t="n">
-        <v>0</v>
+      <c r="BK83" t="inlineStr"/>
+      <c r="BL83" t="n">
+        <v>0.01670336975942162</v>
       </c>
     </row>
     <row r="84">
@@ -9702,8 +9853,9 @@
       <c r="BH84" t="inlineStr"/>
       <c r="BI84" t="inlineStr"/>
       <c r="BJ84" t="inlineStr"/>
-      <c r="BK84" t="n">
-        <v>0</v>
+      <c r="BK84" t="inlineStr"/>
+      <c r="BL84" t="n">
+        <v>0.07017543859649122</v>
       </c>
     </row>
     <row r="85">
@@ -9807,7 +9959,8 @@
       <c r="BH85" t="inlineStr"/>
       <c r="BI85" t="inlineStr"/>
       <c r="BJ85" t="inlineStr"/>
-      <c r="BK85" t="n">
+      <c r="BK85" t="inlineStr"/>
+      <c r="BL85" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9912,8 +10065,9 @@
       <c r="BH86" t="inlineStr"/>
       <c r="BI86" t="inlineStr"/>
       <c r="BJ86" t="inlineStr"/>
-      <c r="BK86" t="n">
-        <v>0</v>
+      <c r="BK86" t="inlineStr"/>
+      <c r="BL86" t="n">
+        <v>0.06627452968916384</v>
       </c>
     </row>
     <row r="87">
@@ -10017,8 +10171,9 @@
       <c r="BH87" t="inlineStr"/>
       <c r="BI87" t="inlineStr"/>
       <c r="BJ87" t="inlineStr"/>
-      <c r="BK87" t="n">
-        <v>0</v>
+      <c r="BK87" t="inlineStr"/>
+      <c r="BL87" t="n">
+        <v>0.01934682286119986</v>
       </c>
     </row>
     <row r="88">
@@ -10122,8 +10277,9 @@
       <c r="BH88" t="inlineStr"/>
       <c r="BI88" t="inlineStr"/>
       <c r="BJ88" t="inlineStr"/>
-      <c r="BK88" t="n">
-        <v>0</v>
+      <c r="BK88" t="inlineStr"/>
+      <c r="BL88" t="n">
+        <v>0.004582484725050916</v>
       </c>
     </row>
     <row r="89">
@@ -10189,30 +10345,92 @@
       <c r="X89" t="n">
         <v>0</v>
       </c>
-      <c r="Y89" t="inlineStr"/>
-      <c r="Z89" t="inlineStr"/>
-      <c r="AA89" t="inlineStr"/>
-      <c r="AB89" t="inlineStr"/>
-      <c r="AC89" t="inlineStr"/>
-      <c r="AD89" t="inlineStr"/>
-      <c r="AE89" t="inlineStr"/>
-      <c r="AF89" t="inlineStr"/>
-      <c r="AG89" t="inlineStr"/>
-      <c r="AH89" t="inlineStr"/>
-      <c r="AI89" t="inlineStr"/>
-      <c r="AJ89" t="inlineStr"/>
-      <c r="AK89" t="inlineStr"/>
-      <c r="AL89" t="inlineStr"/>
-      <c r="AM89" t="inlineStr"/>
-      <c r="AN89" t="inlineStr"/>
-      <c r="AO89" t="inlineStr"/>
-      <c r="AP89" t="inlineStr"/>
-      <c r="AQ89" t="inlineStr"/>
-      <c r="AR89" t="inlineStr"/>
-      <c r="AS89" t="inlineStr"/>
-      <c r="AT89" t="inlineStr"/>
-      <c r="AU89" t="inlineStr"/>
-      <c r="AV89" t="inlineStr"/>
+      <c r="Y89" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI89" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP89" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>May 2025: An education facility was hit by an IED explosion planted by JNIM militants, killing one person and injuring another.</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building </t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="AT89" t="inlineStr">
+        <is>
+          <t>Jama'at Nasr al-Islam wal Muslimin</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>Unspecified IED</t>
+        </is>
+      </c>
+      <c r="AV89" t="inlineStr">
+        <is>
+          <t>Primary School</t>
+        </is>
+      </c>
       <c r="AW89" t="inlineStr"/>
       <c r="AX89" t="inlineStr"/>
       <c r="AY89" t="inlineStr"/>
@@ -10227,8 +10445,9 @@
       <c r="BH89" t="inlineStr"/>
       <c r="BI89" t="inlineStr"/>
       <c r="BJ89" t="inlineStr"/>
-      <c r="BK89" t="n">
-        <v>0</v>
+      <c r="BK89" t="inlineStr"/>
+      <c r="BL89" t="n">
+        <v>0.1157626922632127</v>
       </c>
     </row>
     <row r="90">
@@ -10332,8 +10551,9 @@
       <c r="BH90" t="inlineStr"/>
       <c r="BI90" t="inlineStr"/>
       <c r="BJ90" t="inlineStr"/>
-      <c r="BK90" t="n">
-        <v>0</v>
+      <c r="BK90" t="inlineStr"/>
+      <c r="BL90" t="n">
+        <v>0.08719570898088295</v>
       </c>
     </row>
     <row r="91">
@@ -10430,16 +10650,16 @@
           <t>Centre-Est</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>Koulpelogo</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>1</v>
       </c>
       <c r="BA91" t="n">
         <v>1</v>
       </c>
-      <c r="BB91" t="n">
-        <v>1</v>
+      <c r="BB91" t="inlineStr">
+        <is>
+          <t>BF48</t>
+        </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
@@ -10470,11 +10690,16 @@
       </c>
       <c r="BJ91" t="inlineStr">
         <is>
-          <t>07 May 2025</t>
-        </is>
-      </c>
-      <c r="BK91" t="n">
-        <v>0</v>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="BK91" t="inlineStr">
+        <is>
+          <t>Koulpelogo</t>
+        </is>
+      </c>
+      <c r="BL91" t="n">
+        <v>0.02144542696366984</v>
       </c>
     </row>
     <row r="92">
@@ -10578,8 +10803,9 @@
       <c r="BH92" t="inlineStr"/>
       <c r="BI92" t="inlineStr"/>
       <c r="BJ92" t="inlineStr"/>
-      <c r="BK92" t="n">
-        <v>0</v>
+      <c r="BK92" t="inlineStr"/>
+      <c r="BL92" t="n">
+        <v>0.04659710193908158</v>
       </c>
     </row>
     <row r="93">
@@ -10683,8 +10909,9 @@
       <c r="BH93" t="inlineStr"/>
       <c r="BI93" t="inlineStr"/>
       <c r="BJ93" t="inlineStr"/>
-      <c r="BK93" t="n">
-        <v>0</v>
+      <c r="BK93" t="inlineStr"/>
+      <c r="BL93" t="n">
+        <v>0.01430958088181884</v>
       </c>
     </row>
     <row r="94">
@@ -10788,8 +11015,9 @@
       <c r="BH94" t="inlineStr"/>
       <c r="BI94" t="inlineStr"/>
       <c r="BJ94" t="inlineStr"/>
-      <c r="BK94" t="n">
-        <v>0</v>
+      <c r="BK94" t="inlineStr"/>
+      <c r="BL94" t="n">
+        <v>0.04309915296462382</v>
       </c>
     </row>
     <row r="95">
@@ -10893,8 +11121,9 @@
       <c r="BH95" t="inlineStr"/>
       <c r="BI95" t="inlineStr"/>
       <c r="BJ95" t="inlineStr"/>
-      <c r="BK95" t="n">
-        <v>0</v>
+      <c r="BK95" t="inlineStr"/>
+      <c r="BL95" t="n">
+        <v>0.1083437110834371</v>
       </c>
     </row>
     <row r="96">
@@ -10998,8 +11227,9 @@
       <c r="BH96" t="inlineStr"/>
       <c r="BI96" t="inlineStr"/>
       <c r="BJ96" t="inlineStr"/>
-      <c r="BK96" t="n">
-        <v>0</v>
+      <c r="BK96" t="inlineStr"/>
+      <c r="BL96" t="n">
+        <v>0.008125627681913631</v>
       </c>
     </row>
     <row r="97">
@@ -11103,8 +11333,9 @@
       <c r="BH97" t="inlineStr"/>
       <c r="BI97" t="inlineStr"/>
       <c r="BJ97" t="inlineStr"/>
-      <c r="BK97" t="n">
-        <v>0</v>
+      <c r="BK97" t="inlineStr"/>
+      <c r="BL97" t="n">
+        <v>0.09497479264921126</v>
       </c>
     </row>
     <row r="98">
@@ -11208,8 +11439,9 @@
       <c r="BH98" t="inlineStr"/>
       <c r="BI98" t="inlineStr"/>
       <c r="BJ98" t="inlineStr"/>
-      <c r="BK98" t="n">
-        <v>0</v>
+      <c r="BK98" t="inlineStr"/>
+      <c r="BL98" t="n">
+        <v>0.04298541679933771</v>
       </c>
     </row>
     <row r="99">
@@ -11313,8 +11545,9 @@
       <c r="BH99" t="inlineStr"/>
       <c r="BI99" t="inlineStr"/>
       <c r="BJ99" t="inlineStr"/>
-      <c r="BK99" t="n">
-        <v>0</v>
+      <c r="BK99" t="inlineStr"/>
+      <c r="BL99" t="n">
+        <v>0.08280220805888157</v>
       </c>
     </row>
     <row r="100">
@@ -11418,8 +11651,9 @@
       <c r="BH100" t="inlineStr"/>
       <c r="BI100" t="inlineStr"/>
       <c r="BJ100" t="inlineStr"/>
-      <c r="BK100" t="n">
-        <v>0</v>
+      <c r="BK100" t="inlineStr"/>
+      <c r="BL100" t="n">
+        <v>0.1337702000283154</v>
       </c>
     </row>
     <row r="101">
@@ -11523,8 +11757,9 @@
       <c r="BH101" t="inlineStr"/>
       <c r="BI101" t="inlineStr"/>
       <c r="BJ101" t="inlineStr"/>
-      <c r="BK101" t="n">
-        <v>0</v>
+      <c r="BK101" t="inlineStr"/>
+      <c r="BL101" t="n">
+        <v>0.02003066896683918</v>
       </c>
     </row>
     <row r="102">
@@ -11628,8 +11863,9 @@
       <c r="BH102" t="inlineStr"/>
       <c r="BI102" t="inlineStr"/>
       <c r="BJ102" t="inlineStr"/>
-      <c r="BK102" t="n">
-        <v>0</v>
+      <c r="BK102" t="inlineStr"/>
+      <c r="BL102" t="n">
+        <v>0.1378405398650338</v>
       </c>
     </row>
     <row r="103">
@@ -11733,8 +11969,9 @@
       <c r="BH103" t="inlineStr"/>
       <c r="BI103" t="inlineStr"/>
       <c r="BJ103" t="inlineStr"/>
-      <c r="BK103" t="n">
-        <v>0</v>
+      <c r="BK103" t="inlineStr"/>
+      <c r="BL103" t="n">
+        <v>0.2494726222140695</v>
       </c>
     </row>
     <row r="104">
@@ -11838,8 +12075,9 @@
       <c r="BH104" t="inlineStr"/>
       <c r="BI104" t="inlineStr"/>
       <c r="BJ104" t="inlineStr"/>
-      <c r="BK104" t="n">
-        <v>0</v>
+      <c r="BK104" t="inlineStr"/>
+      <c r="BL104" t="n">
+        <v>0.02288928127656792</v>
       </c>
     </row>
     <row r="105">
@@ -11943,8 +12181,9 @@
       <c r="BH105" t="inlineStr"/>
       <c r="BI105" t="inlineStr"/>
       <c r="BJ105" t="inlineStr"/>
-      <c r="BK105" t="n">
-        <v>0</v>
+      <c r="BK105" t="inlineStr"/>
+      <c r="BL105" t="n">
+        <v>0.4354427353152148</v>
       </c>
     </row>
     <row r="106">
@@ -12048,8 +12287,9 @@
       <c r="BH106" t="inlineStr"/>
       <c r="BI106" t="inlineStr"/>
       <c r="BJ106" t="inlineStr"/>
-      <c r="BK106" t="n">
-        <v>0</v>
+      <c r="BK106" t="inlineStr"/>
+      <c r="BL106" t="n">
+        <v>0.02751241880015285</v>
       </c>
     </row>
     <row r="107">
@@ -12153,8 +12393,9 @@
       <c r="BH107" t="inlineStr"/>
       <c r="BI107" t="inlineStr"/>
       <c r="BJ107" t="inlineStr"/>
-      <c r="BK107" t="n">
-        <v>0</v>
+      <c r="BK107" t="inlineStr"/>
+      <c r="BL107" t="n">
+        <v>0.08924141909431785</v>
       </c>
     </row>
     <row r="108">
@@ -12258,8 +12499,9 @@
       <c r="BH108" t="inlineStr"/>
       <c r="BI108" t="inlineStr"/>
       <c r="BJ108" t="inlineStr"/>
-      <c r="BK108" t="n">
-        <v>0</v>
+      <c r="BK108" t="inlineStr"/>
+      <c r="BL108" t="n">
+        <v>0.2026204960224614</v>
       </c>
     </row>
     <row r="109">
@@ -12363,8 +12605,9 @@
       <c r="BH109" t="inlineStr"/>
       <c r="BI109" t="inlineStr"/>
       <c r="BJ109" t="inlineStr"/>
-      <c r="BK109" t="n">
-        <v>0</v>
+      <c r="BK109" t="inlineStr"/>
+      <c r="BL109" t="n">
+        <v>0.07722513089005235</v>
       </c>
     </row>
     <row r="110">
@@ -12468,8 +12711,9 @@
       <c r="BH110" t="inlineStr"/>
       <c r="BI110" t="inlineStr"/>
       <c r="BJ110" t="inlineStr"/>
-      <c r="BK110" t="n">
-        <v>0</v>
+      <c r="BK110" t="inlineStr"/>
+      <c r="BL110" t="n">
+        <v>0.1948217920196904</v>
       </c>
     </row>
     <row r="111">
@@ -12573,7 +12817,8 @@
       <c r="BH111" t="inlineStr"/>
       <c r="BI111" t="inlineStr"/>
       <c r="BJ111" t="inlineStr"/>
-      <c r="BK111" t="n">
+      <c r="BK111" t="inlineStr"/>
+      <c r="BL111" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12678,8 +12923,9 @@
       <c r="BH112" t="inlineStr"/>
       <c r="BI112" t="inlineStr"/>
       <c r="BJ112" t="inlineStr"/>
-      <c r="BK112" t="n">
-        <v>0</v>
+      <c r="BK112" t="inlineStr"/>
+      <c r="BL112" t="n">
+        <v>0.05152180734232821</v>
       </c>
     </row>
     <row r="113">
@@ -12776,16 +13022,16 @@
           <t>Centre-Nord</t>
         </is>
       </c>
-      <c r="AZ113" t="inlineStr">
-        <is>
-          <t>Namentenga</t>
-        </is>
+      <c r="AZ113" t="n">
+        <v>0</v>
       </c>
       <c r="BA113" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB113" t="n">
         <v>1</v>
+      </c>
+      <c r="BB113" t="inlineStr">
+        <is>
+          <t>BF49</t>
+        </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
@@ -12816,11 +13062,16 @@
       </c>
       <c r="BJ113" t="inlineStr">
         <is>
-          <t>24 January 2024</t>
-        </is>
-      </c>
-      <c r="BK113" t="n">
-        <v>0</v>
+          <t>2024-01-24</t>
+        </is>
+      </c>
+      <c r="BK113" t="inlineStr">
+        <is>
+          <t>Namentenga</t>
+        </is>
+      </c>
+      <c r="BL113" t="n">
+        <v>0.08197581615026349</v>
       </c>
     </row>
     <row r="114">
@@ -12924,8 +13175,9 @@
       <c r="BH114" t="inlineStr"/>
       <c r="BI114" t="inlineStr"/>
       <c r="BJ114" t="inlineStr"/>
-      <c r="BK114" t="n">
-        <v>0</v>
+      <c r="BK114" t="inlineStr"/>
+      <c r="BL114" t="n">
+        <v>0.2362177792979074</v>
       </c>
     </row>
     <row r="115">
@@ -13029,8 +13281,9 @@
       <c r="BH115" t="inlineStr"/>
       <c r="BI115" t="inlineStr"/>
       <c r="BJ115" t="inlineStr"/>
-      <c r="BK115" t="n">
-        <v>0</v>
+      <c r="BK115" t="inlineStr"/>
+      <c r="BL115" t="n">
+        <v>0.02536669542709232</v>
       </c>
     </row>
     <row r="116">
@@ -13134,8 +13387,9 @@
       <c r="BH116" t="inlineStr"/>
       <c r="BI116" t="inlineStr"/>
       <c r="BJ116" t="inlineStr"/>
-      <c r="BK116" t="n">
-        <v>0</v>
+      <c r="BK116" t="inlineStr"/>
+      <c r="BL116" t="n">
+        <v>0.05149647887323944</v>
       </c>
     </row>
     <row r="117">
@@ -13239,8 +13493,9 @@
       <c r="BH117" t="inlineStr"/>
       <c r="BI117" t="inlineStr"/>
       <c r="BJ117" t="inlineStr"/>
-      <c r="BK117" t="n">
-        <v>0</v>
+      <c r="BK117" t="inlineStr"/>
+      <c r="BL117" t="n">
+        <v>0.3566516180751867</v>
       </c>
     </row>
     <row r="118">
@@ -13344,8 +13599,9 @@
       <c r="BH118" t="inlineStr"/>
       <c r="BI118" t="inlineStr"/>
       <c r="BJ118" t="inlineStr"/>
-      <c r="BK118" t="n">
-        <v>0</v>
+      <c r="BK118" t="inlineStr"/>
+      <c r="BL118" t="n">
+        <v>0.5890292062665452</v>
       </c>
     </row>
     <row r="119">
@@ -13449,8 +13705,9 @@
       <c r="BH119" t="inlineStr"/>
       <c r="BI119" t="inlineStr"/>
       <c r="BJ119" t="inlineStr"/>
-      <c r="BK119" t="n">
-        <v>0</v>
+      <c r="BK119" t="inlineStr"/>
+      <c r="BL119" t="n">
+        <v>0.01233686124277644</v>
       </c>
     </row>
     <row r="120">
@@ -13554,8 +13811,9 @@
       <c r="BH120" t="inlineStr"/>
       <c r="BI120" t="inlineStr"/>
       <c r="BJ120" t="inlineStr"/>
-      <c r="BK120" t="n">
-        <v>0</v>
+      <c r="BK120" t="inlineStr"/>
+      <c r="BL120" t="n">
+        <v>0.8099330944445836</v>
       </c>
     </row>
     <row r="121">
@@ -13659,8 +13917,9 @@
       <c r="BH121" t="inlineStr"/>
       <c r="BI121" t="inlineStr"/>
       <c r="BJ121" t="inlineStr"/>
-      <c r="BK121" t="n">
-        <v>0</v>
+      <c r="BK121" t="inlineStr"/>
+      <c r="BL121" t="n">
+        <v>0.07976690416647006</v>
       </c>
     </row>
     <row r="122">
@@ -13764,7 +14023,8 @@
       <c r="BH122" t="inlineStr"/>
       <c r="BI122" t="inlineStr"/>
       <c r="BJ122" t="inlineStr"/>
-      <c r="BK122" t="n">
+      <c r="BK122" t="inlineStr"/>
+      <c r="BL122" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13862,16 +14122,16 @@
           <t>Centre-Nord</t>
         </is>
       </c>
-      <c r="AZ123" t="inlineStr">
-        <is>
-          <t>Sanmatenga</t>
-        </is>
+      <c r="AZ123" t="n">
+        <v>0</v>
       </c>
       <c r="BA123" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB123" t="n">
         <v>1</v>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>BF49</t>
+        </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
@@ -13902,11 +14162,16 @@
       </c>
       <c r="BJ123" t="inlineStr">
         <is>
-          <t>06 August 2024</t>
-        </is>
-      </c>
-      <c r="BK123" t="n">
-        <v>0</v>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="BK123" t="inlineStr">
+        <is>
+          <t>Sanmatenga</t>
+        </is>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.549905162842339</v>
       </c>
     </row>
     <row r="124">
@@ -14010,8 +14275,9 @@
       <c r="BH124" t="inlineStr"/>
       <c r="BI124" t="inlineStr"/>
       <c r="BJ124" t="inlineStr"/>
-      <c r="BK124" t="n">
-        <v>0</v>
+      <c r="BK124" t="inlineStr"/>
+      <c r="BL124" t="n">
+        <v>0.08301336200276455</v>
       </c>
     </row>
     <row r="125">
@@ -14115,8 +14381,9 @@
       <c r="BH125" t="inlineStr"/>
       <c r="BI125" t="inlineStr"/>
       <c r="BJ125" t="inlineStr"/>
-      <c r="BK125" t="n">
-        <v>0</v>
+      <c r="BK125" t="inlineStr"/>
+      <c r="BL125" t="n">
+        <v>0.1340665272248836</v>
       </c>
     </row>
     <row r="126">
@@ -14220,7 +14487,8 @@
       <c r="BH126" t="inlineStr"/>
       <c r="BI126" t="inlineStr"/>
       <c r="BJ126" t="inlineStr"/>
-      <c r="BK126" t="n">
+      <c r="BK126" t="inlineStr"/>
+      <c r="BL126" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14325,8 +14593,9 @@
       <c r="BH127" t="inlineStr"/>
       <c r="BI127" t="inlineStr"/>
       <c r="BJ127" t="inlineStr"/>
-      <c r="BK127" t="n">
-        <v>0</v>
+      <c r="BK127" t="inlineStr"/>
+      <c r="BL127" t="n">
+        <v>0.6692476328186949</v>
       </c>
     </row>
     <row r="128">
@@ -14430,8 +14699,9 @@
       <c r="BH128" t="inlineStr"/>
       <c r="BI128" t="inlineStr"/>
       <c r="BJ128" t="inlineStr"/>
-      <c r="BK128" t="n">
-        <v>0</v>
+      <c r="BK128" t="inlineStr"/>
+      <c r="BL128" t="n">
+        <v>0.02326122354035822</v>
       </c>
     </row>
     <row r="129">
@@ -14590,16 +14860,16 @@
           <t>Centre-Nord</t>
         </is>
       </c>
-      <c r="AZ129" t="inlineStr">
-        <is>
-          <t>Sanmatenga</t>
-        </is>
+      <c r="AZ129" t="n">
+        <v>1</v>
       </c>
       <c r="BA129" t="n">
         <v>1</v>
       </c>
-      <c r="BB129" t="n">
-        <v>1</v>
+      <c r="BB129" t="inlineStr">
+        <is>
+          <t>BF49</t>
+        </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
@@ -14634,11 +14904,16 @@
       </c>
       <c r="BJ129" t="inlineStr">
         <is>
-          <t>27 July 2024</t>
-        </is>
-      </c>
-      <c r="BK129" t="n">
-        <v>0</v>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="BK129" t="inlineStr">
+        <is>
+          <t>Sanmatenga</t>
+        </is>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.6604837091055061</v>
       </c>
     </row>
     <row r="130">
@@ -14742,8 +15017,9 @@
       <c r="BH130" t="inlineStr"/>
       <c r="BI130" t="inlineStr"/>
       <c r="BJ130" t="inlineStr"/>
-      <c r="BK130" t="n">
-        <v>0</v>
+      <c r="BK130" t="inlineStr"/>
+      <c r="BL130" t="n">
+        <v>0.0219915733223718</v>
       </c>
     </row>
     <row r="131">
@@ -14847,8 +15123,9 @@
       <c r="BH131" t="inlineStr"/>
       <c r="BI131" t="inlineStr"/>
       <c r="BJ131" t="inlineStr"/>
-      <c r="BK131" t="n">
-        <v>0</v>
+      <c r="BK131" t="inlineStr"/>
+      <c r="BL131" t="n">
+        <v>0.009721806760394854</v>
       </c>
     </row>
     <row r="132">
@@ -14952,7 +15229,8 @@
       <c r="BH132" t="inlineStr"/>
       <c r="BI132" t="inlineStr"/>
       <c r="BJ132" t="inlineStr"/>
-      <c r="BK132" t="n">
+      <c r="BK132" t="inlineStr"/>
+      <c r="BL132" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15057,7 +15335,8 @@
       <c r="BH133" t="inlineStr"/>
       <c r="BI133" t="inlineStr"/>
       <c r="BJ133" t="inlineStr"/>
-      <c r="BK133" t="n">
+      <c r="BK133" t="inlineStr"/>
+      <c r="BL133" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15162,8 +15441,9 @@
       <c r="BH134" t="inlineStr"/>
       <c r="BI134" t="inlineStr"/>
       <c r="BJ134" t="inlineStr"/>
-      <c r="BK134" t="n">
-        <v>0</v>
+      <c r="BK134" t="inlineStr"/>
+      <c r="BL134" t="n">
+        <v>0.002797271433478923</v>
       </c>
     </row>
     <row r="135">
@@ -15267,8 +15547,9 @@
       <c r="BH135" t="inlineStr"/>
       <c r="BI135" t="inlineStr"/>
       <c r="BJ135" t="inlineStr"/>
-      <c r="BK135" t="n">
-        <v>0</v>
+      <c r="BK135" t="inlineStr"/>
+      <c r="BL135" t="n">
+        <v>0.01469837705420027</v>
       </c>
     </row>
     <row r="136">
@@ -15372,8 +15653,9 @@
       <c r="BH136" t="inlineStr"/>
       <c r="BI136" t="inlineStr"/>
       <c r="BJ136" t="inlineStr"/>
-      <c r="BK136" t="n">
-        <v>0</v>
+      <c r="BK136" t="inlineStr"/>
+      <c r="BL136" t="n">
+        <v>0.002332089552238806</v>
       </c>
     </row>
     <row r="137">
@@ -15477,7 +15759,8 @@
       <c r="BH137" t="inlineStr"/>
       <c r="BI137" t="inlineStr"/>
       <c r="BJ137" t="inlineStr"/>
-      <c r="BK137" t="n">
+      <c r="BK137" t="inlineStr"/>
+      <c r="BL137" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15582,8 +15865,9 @@
       <c r="BH138" t="inlineStr"/>
       <c r="BI138" t="inlineStr"/>
       <c r="BJ138" t="inlineStr"/>
-      <c r="BK138" t="n">
-        <v>0</v>
+      <c r="BK138" t="inlineStr"/>
+      <c r="BL138" t="n">
+        <v>0.004906971989368228</v>
       </c>
     </row>
     <row r="139">
@@ -15687,8 +15971,9 @@
       <c r="BH139" t="inlineStr"/>
       <c r="BI139" t="inlineStr"/>
       <c r="BJ139" t="inlineStr"/>
-      <c r="BK139" t="n">
-        <v>0</v>
+      <c r="BK139" t="inlineStr"/>
+      <c r="BL139" t="n">
+        <v>0.003573697585768742</v>
       </c>
     </row>
     <row r="140">
@@ -15792,8 +16077,9 @@
       <c r="BH140" t="inlineStr"/>
       <c r="BI140" t="inlineStr"/>
       <c r="BJ140" t="inlineStr"/>
-      <c r="BK140" t="n">
-        <v>0</v>
+      <c r="BK140" t="inlineStr"/>
+      <c r="BL140" t="n">
+        <v>0.0055286800276434</v>
       </c>
     </row>
     <row r="141">
@@ -15897,8 +16183,9 @@
       <c r="BH141" t="inlineStr"/>
       <c r="BI141" t="inlineStr"/>
       <c r="BJ141" t="inlineStr"/>
-      <c r="BK141" t="n">
-        <v>0</v>
+      <c r="BK141" t="inlineStr"/>
+      <c r="BL141" t="n">
+        <v>0.002894356005788712</v>
       </c>
     </row>
     <row r="142">
@@ -16002,8 +16289,9 @@
       <c r="BH142" t="inlineStr"/>
       <c r="BI142" t="inlineStr"/>
       <c r="BJ142" t="inlineStr"/>
-      <c r="BK142" t="n">
-        <v>0</v>
+      <c r="BK142" t="inlineStr"/>
+      <c r="BL142" t="n">
+        <v>0.004192265992049151</v>
       </c>
     </row>
     <row r="143">
@@ -16107,8 +16395,9 @@
       <c r="BH143" t="inlineStr"/>
       <c r="BI143" t="inlineStr"/>
       <c r="BJ143" t="inlineStr"/>
-      <c r="BK143" t="n">
-        <v>0</v>
+      <c r="BK143" t="inlineStr"/>
+      <c r="BL143" t="n">
+        <v>0.01002252252252252</v>
       </c>
     </row>
     <row r="144">
@@ -16212,8 +16501,9 @@
       <c r="BH144" t="inlineStr"/>
       <c r="BI144" t="inlineStr"/>
       <c r="BJ144" t="inlineStr"/>
-      <c r="BK144" t="n">
-        <v>0</v>
+      <c r="BK144" t="inlineStr"/>
+      <c r="BL144" t="n">
+        <v>0.0005735589331803843</v>
       </c>
     </row>
     <row r="145">
@@ -16317,8 +16607,9 @@
       <c r="BH145" t="inlineStr"/>
       <c r="BI145" t="inlineStr"/>
       <c r="BJ145" t="inlineStr"/>
-      <c r="BK145" t="n">
-        <v>0</v>
+      <c r="BK145" t="inlineStr"/>
+      <c r="BL145" t="n">
+        <v>7.635336336565625e-05</v>
       </c>
     </row>
     <row r="146">
@@ -16422,8 +16713,9 @@
       <c r="BH146" t="inlineStr"/>
       <c r="BI146" t="inlineStr"/>
       <c r="BJ146" t="inlineStr"/>
-      <c r="BK146" t="n">
-        <v>0</v>
+      <c r="BK146" t="inlineStr"/>
+      <c r="BL146" t="n">
+        <v>0.0501813784764208</v>
       </c>
     </row>
     <row r="147">
@@ -16527,8 +16819,9 @@
       <c r="BH147" t="inlineStr"/>
       <c r="BI147" t="inlineStr"/>
       <c r="BJ147" t="inlineStr"/>
-      <c r="BK147" t="n">
-        <v>0</v>
+      <c r="BK147" t="inlineStr"/>
+      <c r="BL147" t="n">
+        <v>0.05153236025719247</v>
       </c>
     </row>
     <row r="148">
@@ -16632,7 +16925,8 @@
       <c r="BH148" t="inlineStr"/>
       <c r="BI148" t="inlineStr"/>
       <c r="BJ148" t="inlineStr"/>
-      <c r="BK148" t="n">
+      <c r="BK148" t="inlineStr"/>
+      <c r="BL148" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16737,7 +17031,8 @@
       <c r="BH149" t="inlineStr"/>
       <c r="BI149" t="inlineStr"/>
       <c r="BJ149" t="inlineStr"/>
-      <c r="BK149" t="n">
+      <c r="BK149" t="inlineStr"/>
+      <c r="BL149" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16842,8 +17137,9 @@
       <c r="BH150" t="inlineStr"/>
       <c r="BI150" t="inlineStr"/>
       <c r="BJ150" t="inlineStr"/>
-      <c r="BK150" t="n">
-        <v>0</v>
+      <c r="BK150" t="inlineStr"/>
+      <c r="BL150" t="n">
+        <v>0.0009221311475409836</v>
       </c>
     </row>
     <row r="151">
@@ -16947,8 +17243,9 @@
       <c r="BH151" t="inlineStr"/>
       <c r="BI151" t="inlineStr"/>
       <c r="BJ151" t="inlineStr"/>
-      <c r="BK151" t="n">
-        <v>0</v>
+      <c r="BK151" t="inlineStr"/>
+      <c r="BL151" t="n">
+        <v>0.04514293105678437</v>
       </c>
     </row>
     <row r="152">
@@ -17052,8 +17349,9 @@
       <c r="BH152" t="inlineStr"/>
       <c r="BI152" t="inlineStr"/>
       <c r="BJ152" t="inlineStr"/>
-      <c r="BK152" t="n">
-        <v>0</v>
+      <c r="BK152" t="inlineStr"/>
+      <c r="BL152" t="n">
+        <v>0.04792926942764077</v>
       </c>
     </row>
     <row r="153">
@@ -17157,8 +17455,9 @@
       <c r="BH153" t="inlineStr"/>
       <c r="BI153" t="inlineStr"/>
       <c r="BJ153" t="inlineStr"/>
-      <c r="BK153" t="n">
-        <v>0</v>
+      <c r="BK153" t="inlineStr"/>
+      <c r="BL153" t="n">
+        <v>0.001134930643127364</v>
       </c>
     </row>
     <row r="154">
@@ -17262,8 +17561,9 @@
       <c r="BH154" t="inlineStr"/>
       <c r="BI154" t="inlineStr"/>
       <c r="BJ154" t="inlineStr"/>
-      <c r="BK154" t="n">
-        <v>0</v>
+      <c r="BK154" t="inlineStr"/>
+      <c r="BL154" t="n">
+        <v>0.1532109094860372</v>
       </c>
     </row>
     <row r="155">
@@ -17367,8 +17667,9 @@
       <c r="BH155" t="inlineStr"/>
       <c r="BI155" t="inlineStr"/>
       <c r="BJ155" t="inlineStr"/>
-      <c r="BK155" t="n">
-        <v>0</v>
+      <c r="BK155" t="inlineStr"/>
+      <c r="BL155" t="n">
+        <v>0.04784470974209423</v>
       </c>
     </row>
     <row r="156">
@@ -17472,8 +17773,9 @@
       <c r="BH156" t="inlineStr"/>
       <c r="BI156" t="inlineStr"/>
       <c r="BJ156" t="inlineStr"/>
-      <c r="BK156" t="n">
-        <v>0</v>
+      <c r="BK156" t="inlineStr"/>
+      <c r="BL156" t="n">
+        <v>0.1049300169385754</v>
       </c>
     </row>
     <row r="157">
@@ -17577,8 +17879,9 @@
       <c r="BH157" t="inlineStr"/>
       <c r="BI157" t="inlineStr"/>
       <c r="BJ157" t="inlineStr"/>
-      <c r="BK157" t="n">
-        <v>0</v>
+      <c r="BK157" t="inlineStr"/>
+      <c r="BL157" t="n">
+        <v>0.0457776688319647</v>
       </c>
     </row>
     <row r="158">
@@ -17682,8 +17985,9 @@
       <c r="BH158" t="inlineStr"/>
       <c r="BI158" t="inlineStr"/>
       <c r="BJ158" t="inlineStr"/>
-      <c r="BK158" t="n">
-        <v>0</v>
+      <c r="BK158" t="inlineStr"/>
+      <c r="BL158" t="n">
+        <v>0.05143721633888049</v>
       </c>
     </row>
     <row r="159">
@@ -17787,8 +18091,9 @@
       <c r="BH159" t="inlineStr"/>
       <c r="BI159" t="inlineStr"/>
       <c r="BJ159" t="inlineStr"/>
-      <c r="BK159" t="n">
-        <v>0</v>
+      <c r="BK159" t="inlineStr"/>
+      <c r="BL159" t="n">
+        <v>0.01896519977904621</v>
       </c>
     </row>
     <row r="160">
@@ -17892,8 +18197,9 @@
       <c r="BH160" t="inlineStr"/>
       <c r="BI160" t="inlineStr"/>
       <c r="BJ160" t="inlineStr"/>
-      <c r="BK160" t="n">
-        <v>0</v>
+      <c r="BK160" t="inlineStr"/>
+      <c r="BL160" t="n">
+        <v>0.01211462297118894</v>
       </c>
     </row>
     <row r="161">
@@ -17997,8 +18303,9 @@
       <c r="BH161" t="inlineStr"/>
       <c r="BI161" t="inlineStr"/>
       <c r="BJ161" t="inlineStr"/>
-      <c r="BK161" t="n">
-        <v>0</v>
+      <c r="BK161" t="inlineStr"/>
+      <c r="BL161" t="n">
+        <v>0.00751405856117898</v>
       </c>
     </row>
     <row r="162">
@@ -18102,8 +18409,9 @@
       <c r="BH162" t="inlineStr"/>
       <c r="BI162" t="inlineStr"/>
       <c r="BJ162" t="inlineStr"/>
-      <c r="BK162" t="n">
-        <v>0</v>
+      <c r="BK162" t="inlineStr"/>
+      <c r="BL162" t="n">
+        <v>0.03556072051133062</v>
       </c>
     </row>
     <row r="163">
@@ -18207,8 +18515,9 @@
       <c r="BH163" t="inlineStr"/>
       <c r="BI163" t="inlineStr"/>
       <c r="BJ163" t="inlineStr"/>
-      <c r="BK163" t="n">
-        <v>0</v>
+      <c r="BK163" t="inlineStr"/>
+      <c r="BL163" t="n">
+        <v>0.02671519281400031</v>
       </c>
     </row>
     <row r="164">
@@ -18312,7 +18621,8 @@
       <c r="BH164" t="inlineStr"/>
       <c r="BI164" t="inlineStr"/>
       <c r="BJ164" t="inlineStr"/>
-      <c r="BK164" t="n">
+      <c r="BK164" t="inlineStr"/>
+      <c r="BL164" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18417,8 +18727,9 @@
       <c r="BH165" t="inlineStr"/>
       <c r="BI165" t="inlineStr"/>
       <c r="BJ165" t="inlineStr"/>
-      <c r="BK165" t="n">
-        <v>0</v>
+      <c r="BK165" t="inlineStr"/>
+      <c r="BL165" t="n">
+        <v>0.04838782616560394</v>
       </c>
     </row>
     <row r="166">
@@ -18522,8 +18833,9 @@
       <c r="BH166" t="inlineStr"/>
       <c r="BI166" t="inlineStr"/>
       <c r="BJ166" t="inlineStr"/>
-      <c r="BK166" t="n">
-        <v>0</v>
+      <c r="BK166" t="inlineStr"/>
+      <c r="BL166" t="n">
+        <v>0.001182732111176819</v>
       </c>
     </row>
     <row r="167">
@@ -18627,8 +18939,9 @@
       <c r="BH167" t="inlineStr"/>
       <c r="BI167" t="inlineStr"/>
       <c r="BJ167" t="inlineStr"/>
-      <c r="BK167" t="n">
-        <v>0</v>
+      <c r="BK167" t="inlineStr"/>
+      <c r="BL167" t="n">
+        <v>0.002255427121511136</v>
       </c>
     </row>
     <row r="168">
@@ -18732,8 +19045,9 @@
       <c r="BH168" t="inlineStr"/>
       <c r="BI168" t="inlineStr"/>
       <c r="BJ168" t="inlineStr"/>
-      <c r="BK168" t="n">
-        <v>0</v>
+      <c r="BK168" t="inlineStr"/>
+      <c r="BL168" t="n">
+        <v>0.1209832426432768</v>
       </c>
     </row>
     <row r="169">
@@ -18837,8 +19151,9 @@
       <c r="BH169" t="inlineStr"/>
       <c r="BI169" t="inlineStr"/>
       <c r="BJ169" t="inlineStr"/>
-      <c r="BK169" t="n">
-        <v>0</v>
+      <c r="BK169" t="inlineStr"/>
+      <c r="BL169" t="n">
+        <v>0.008182050626438252</v>
       </c>
     </row>
     <row r="170">
@@ -18942,8 +19257,9 @@
       <c r="BH170" t="inlineStr"/>
       <c r="BI170" t="inlineStr"/>
       <c r="BJ170" t="inlineStr"/>
-      <c r="BK170" t="n">
-        <v>0</v>
+      <c r="BK170" t="inlineStr"/>
+      <c r="BL170" t="n">
+        <v>0.02529823118058412</v>
       </c>
     </row>
     <row r="171">
@@ -19047,8 +19363,9 @@
       <c r="BH171" t="inlineStr"/>
       <c r="BI171" t="inlineStr"/>
       <c r="BJ171" t="inlineStr"/>
-      <c r="BK171" t="n">
-        <v>0</v>
+      <c r="BK171" t="inlineStr"/>
+      <c r="BL171" t="n">
+        <v>0.02160148975791434</v>
       </c>
     </row>
     <row r="172">
@@ -19152,8 +19469,9 @@
       <c r="BH172" t="inlineStr"/>
       <c r="BI172" t="inlineStr"/>
       <c r="BJ172" t="inlineStr"/>
-      <c r="BK172" t="n">
-        <v>0</v>
+      <c r="BK172" t="inlineStr"/>
+      <c r="BL172" t="n">
+        <v>0.0005612722170252573</v>
       </c>
     </row>
     <row r="173">
@@ -19257,8 +19575,9 @@
       <c r="BH173" t="inlineStr"/>
       <c r="BI173" t="inlineStr"/>
       <c r="BJ173" t="inlineStr"/>
-      <c r="BK173" t="n">
-        <v>0</v>
+      <c r="BK173" t="inlineStr"/>
+      <c r="BL173" t="n">
+        <v>0.005294636729091087</v>
       </c>
     </row>
     <row r="174">
@@ -19362,8 +19681,9 @@
       <c r="BH174" t="inlineStr"/>
       <c r="BI174" t="inlineStr"/>
       <c r="BJ174" t="inlineStr"/>
-      <c r="BK174" t="n">
-        <v>0</v>
+      <c r="BK174" t="inlineStr"/>
+      <c r="BL174" t="n">
+        <v>0.01154586273252085</v>
       </c>
     </row>
     <row r="175">
@@ -19467,8 +19787,9 @@
       <c r="BH175" t="inlineStr"/>
       <c r="BI175" t="inlineStr"/>
       <c r="BJ175" t="inlineStr"/>
-      <c r="BK175" t="n">
-        <v>0</v>
+      <c r="BK175" t="inlineStr"/>
+      <c r="BL175" t="n">
+        <v>0.001137884872824632</v>
       </c>
     </row>
     <row r="176">
@@ -19572,8 +19893,9 @@
       <c r="BH176" t="inlineStr"/>
       <c r="BI176" t="inlineStr"/>
       <c r="BJ176" t="inlineStr"/>
-      <c r="BK176" t="n">
-        <v>0</v>
+      <c r="BK176" t="inlineStr"/>
+      <c r="BL176" t="n">
+        <v>0.06204692493569257</v>
       </c>
     </row>
     <row r="177">
@@ -19677,8 +19999,9 @@
       <c r="BH177" t="inlineStr"/>
       <c r="BI177" t="inlineStr"/>
       <c r="BJ177" t="inlineStr"/>
-      <c r="BK177" t="n">
-        <v>0</v>
+      <c r="BK177" t="inlineStr"/>
+      <c r="BL177" t="n">
+        <v>0.002699784017278618</v>
       </c>
     </row>
     <row r="178">
@@ -19782,8 +20105,9 @@
       <c r="BH178" t="inlineStr"/>
       <c r="BI178" t="inlineStr"/>
       <c r="BJ178" t="inlineStr"/>
-      <c r="BK178" t="n">
-        <v>0</v>
+      <c r="BK178" t="inlineStr"/>
+      <c r="BL178" t="n">
+        <v>0.0007589812784617979</v>
       </c>
     </row>
     <row r="179">
@@ -19887,8 +20211,9 @@
       <c r="BH179" t="inlineStr"/>
       <c r="BI179" t="inlineStr"/>
       <c r="BJ179" t="inlineStr"/>
-      <c r="BK179" t="n">
-        <v>0</v>
+      <c r="BK179" t="inlineStr"/>
+      <c r="BL179" t="n">
+        <v>0.0003766478342749529</v>
       </c>
     </row>
     <row r="180">
@@ -19992,8 +20317,9 @@
       <c r="BH180" t="inlineStr"/>
       <c r="BI180" t="inlineStr"/>
       <c r="BJ180" t="inlineStr"/>
-      <c r="BK180" t="n">
-        <v>0</v>
+      <c r="BK180" t="inlineStr"/>
+      <c r="BL180" t="n">
+        <v>0.001272842985725975</v>
       </c>
     </row>
     <row r="181">
@@ -20097,8 +20423,9 @@
       <c r="BH181" t="inlineStr"/>
       <c r="BI181" t="inlineStr"/>
       <c r="BJ181" t="inlineStr"/>
-      <c r="BK181" t="n">
-        <v>0</v>
+      <c r="BK181" t="inlineStr"/>
+      <c r="BL181" t="n">
+        <v>0.01930962499068068</v>
       </c>
     </row>
     <row r="182">
@@ -20202,8 +20529,9 @@
       <c r="BH182" t="inlineStr"/>
       <c r="BI182" t="inlineStr"/>
       <c r="BJ182" t="inlineStr"/>
-      <c r="BK182" t="n">
-        <v>0</v>
+      <c r="BK182" t="inlineStr"/>
+      <c r="BL182" t="n">
+        <v>0.02338320179055248</v>
       </c>
     </row>
     <row r="183">
@@ -20307,8 +20635,9 @@
       <c r="BH183" t="inlineStr"/>
       <c r="BI183" t="inlineStr"/>
       <c r="BJ183" t="inlineStr"/>
-      <c r="BK183" t="n">
-        <v>0</v>
+      <c r="BK183" t="inlineStr"/>
+      <c r="BL183" t="n">
+        <v>0.04188351920693928</v>
       </c>
     </row>
     <row r="184">
@@ -20412,8 +20741,9 @@
       <c r="BH184" t="inlineStr"/>
       <c r="BI184" t="inlineStr"/>
       <c r="BJ184" t="inlineStr"/>
-      <c r="BK184" t="n">
-        <v>0</v>
+      <c r="BK184" t="inlineStr"/>
+      <c r="BL184" t="n">
+        <v>0.003212066196494658</v>
       </c>
     </row>
     <row r="185">
@@ -20517,8 +20847,9 @@
       <c r="BH185" t="inlineStr"/>
       <c r="BI185" t="inlineStr"/>
       <c r="BJ185" t="inlineStr"/>
-      <c r="BK185" t="n">
-        <v>0</v>
+      <c r="BK185" t="inlineStr"/>
+      <c r="BL185" t="n">
+        <v>0.003214658844330145</v>
       </c>
     </row>
     <row r="186">
@@ -20622,8 +20953,9 @@
       <c r="BH186" t="inlineStr"/>
       <c r="BI186" t="inlineStr"/>
       <c r="BJ186" t="inlineStr"/>
-      <c r="BK186" t="n">
-        <v>0</v>
+      <c r="BK186" t="inlineStr"/>
+      <c r="BL186" t="n">
+        <v>0.004266546903946556</v>
       </c>
     </row>
     <row r="187">
@@ -20727,8 +21059,9 @@
       <c r="BH187" t="inlineStr"/>
       <c r="BI187" t="inlineStr"/>
       <c r="BJ187" t="inlineStr"/>
-      <c r="BK187" t="n">
-        <v>0</v>
+      <c r="BK187" t="inlineStr"/>
+      <c r="BL187" t="n">
+        <v>0.00122053060962292</v>
       </c>
     </row>
     <row r="188">
@@ -20832,8 +21165,9 @@
       <c r="BH188" t="inlineStr"/>
       <c r="BI188" t="inlineStr"/>
       <c r="BJ188" t="inlineStr"/>
-      <c r="BK188" t="n">
-        <v>0</v>
+      <c r="BK188" t="inlineStr"/>
+      <c r="BL188" t="n">
+        <v>0.09183248255026566</v>
       </c>
     </row>
     <row r="189">
@@ -20999,8 +21333,9 @@
       <c r="BH189" t="inlineStr"/>
       <c r="BI189" t="inlineStr"/>
       <c r="BJ189" t="inlineStr"/>
-      <c r="BK189" t="n">
-        <v>0</v>
+      <c r="BK189" t="inlineStr"/>
+      <c r="BL189" t="n">
+        <v>0.8209034109141703</v>
       </c>
     </row>
     <row r="190">
@@ -21104,8 +21439,9 @@
       <c r="BH190" t="inlineStr"/>
       <c r="BI190" t="inlineStr"/>
       <c r="BJ190" t="inlineStr"/>
-      <c r="BK190" t="n">
-        <v>0</v>
+      <c r="BK190" t="inlineStr"/>
+      <c r="BL190" t="n">
+        <v>0.02477187405803853</v>
       </c>
     </row>
     <row r="191">
@@ -21209,8 +21545,9 @@
       <c r="BH191" t="inlineStr"/>
       <c r="BI191" t="inlineStr"/>
       <c r="BJ191" t="inlineStr"/>
-      <c r="BK191" t="n">
-        <v>0</v>
+      <c r="BK191" t="inlineStr"/>
+      <c r="BL191" t="n">
+        <v>0.01130753304666348</v>
       </c>
     </row>
     <row r="192">
@@ -21314,8 +21651,9 @@
       <c r="BH192" t="inlineStr"/>
       <c r="BI192" t="inlineStr"/>
       <c r="BJ192" t="inlineStr"/>
-      <c r="BK192" t="n">
-        <v>0</v>
+      <c r="BK192" t="inlineStr"/>
+      <c r="BL192" t="n">
+        <v>0.1278326554328879</v>
       </c>
     </row>
     <row r="193">
@@ -21412,16 +21750,16 @@
           <t>Est</t>
         </is>
       </c>
-      <c r="AZ193" t="inlineStr">
-        <is>
-          <t>Gnagna</t>
-        </is>
+      <c r="AZ193" t="n">
+        <v>1</v>
       </c>
       <c r="BA193" t="n">
         <v>1</v>
       </c>
-      <c r="BB193" t="n">
-        <v>1</v>
+      <c r="BB193" t="inlineStr">
+        <is>
+          <t>BF52</t>
+        </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
@@ -21456,11 +21794,16 @@
       </c>
       <c r="BJ193" t="inlineStr">
         <is>
-          <t>04 October 2024</t>
-        </is>
-      </c>
-      <c r="BK193" t="n">
-        <v>0</v>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="BK193" t="inlineStr">
+        <is>
+          <t>Gnagna</t>
+        </is>
+      </c>
+      <c r="BL193" t="n">
+        <v>0.4610195834628536</v>
       </c>
     </row>
     <row r="194">
@@ -21564,8 +21907,9 @@
       <c r="BH194" t="inlineStr"/>
       <c r="BI194" t="inlineStr"/>
       <c r="BJ194" t="inlineStr"/>
-      <c r="BK194" t="n">
-        <v>0</v>
+      <c r="BK194" t="inlineStr"/>
+      <c r="BL194" t="n">
+        <v>0.02265542676501581</v>
       </c>
     </row>
     <row r="195">
@@ -21669,8 +22013,9 @@
       <c r="BH195" t="inlineStr"/>
       <c r="BI195" t="inlineStr"/>
       <c r="BJ195" t="inlineStr"/>
-      <c r="BK195" t="n">
-        <v>0</v>
+      <c r="BK195" t="inlineStr"/>
+      <c r="BL195" t="n">
+        <v>0.05560184170138128</v>
       </c>
     </row>
     <row r="196">
@@ -21767,16 +22112,16 @@
           <t>Est</t>
         </is>
       </c>
-      <c r="AZ196" t="inlineStr">
-        <is>
-          <t>Gourma</t>
-        </is>
+      <c r="AZ196" t="n">
+        <v>10</v>
       </c>
       <c r="BA196" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB196" t="n">
         <v>1</v>
+      </c>
+      <c r="BB196" t="inlineStr">
+        <is>
+          <t>BF52</t>
+        </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
@@ -21807,11 +22152,16 @@
       </c>
       <c r="BJ196" t="inlineStr">
         <is>
-          <t>28 April 2025</t>
-        </is>
-      </c>
-      <c r="BK196" t="n">
-        <v>0</v>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="BK196" t="inlineStr">
+        <is>
+          <t>Gourma</t>
+        </is>
+      </c>
+      <c r="BL196" t="n">
+        <v>0.08853754940711463</v>
       </c>
     </row>
     <row r="197">
@@ -21915,8 +22265,9 @@
       <c r="BH197" t="inlineStr"/>
       <c r="BI197" t="inlineStr"/>
       <c r="BJ197" t="inlineStr"/>
-      <c r="BK197" t="n">
-        <v>0</v>
+      <c r="BK197" t="inlineStr"/>
+      <c r="BL197" t="n">
+        <v>0.6569035506911258</v>
       </c>
     </row>
     <row r="198">
@@ -22020,8 +22371,9 @@
       <c r="BH198" t="inlineStr"/>
       <c r="BI198" t="inlineStr"/>
       <c r="BJ198" t="inlineStr"/>
-      <c r="BK198" t="n">
-        <v>0</v>
+      <c r="BK198" t="inlineStr"/>
+      <c r="BL198" t="n">
+        <v>0.1275530115779888</v>
       </c>
     </row>
     <row r="199">
@@ -22187,8 +22539,9 @@
       <c r="BH199" t="inlineStr"/>
       <c r="BI199" t="inlineStr"/>
       <c r="BJ199" t="inlineStr"/>
-      <c r="BK199" t="n">
-        <v>0</v>
+      <c r="BK199" t="inlineStr"/>
+      <c r="BL199" t="n">
+        <v>0.3055480084768788</v>
       </c>
     </row>
     <row r="200">
@@ -22292,8 +22645,9 @@
       <c r="BH200" t="inlineStr"/>
       <c r="BI200" t="inlineStr"/>
       <c r="BJ200" t="inlineStr"/>
-      <c r="BK200" t="n">
-        <v>0</v>
+      <c r="BK200" t="inlineStr"/>
+      <c r="BL200" t="n">
+        <v>0.02766108705486977</v>
       </c>
     </row>
     <row r="201">
@@ -22397,7 +22751,8 @@
       <c r="BH201" t="inlineStr"/>
       <c r="BI201" t="inlineStr"/>
       <c r="BJ201" t="inlineStr"/>
-      <c r="BK201" t="n">
+      <c r="BK201" t="inlineStr"/>
+      <c r="BL201" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22502,8 +22857,9 @@
       <c r="BH202" t="inlineStr"/>
       <c r="BI202" t="inlineStr"/>
       <c r="BJ202" t="inlineStr"/>
-      <c r="BK202" t="n">
-        <v>0</v>
+      <c r="BK202" t="inlineStr"/>
+      <c r="BL202" t="n">
+        <v>0.3071297989031079</v>
       </c>
     </row>
     <row r="203">
@@ -22607,8 +22963,9 @@
       <c r="BH203" t="inlineStr"/>
       <c r="BI203" t="inlineStr"/>
       <c r="BJ203" t="inlineStr"/>
-      <c r="BK203" t="n">
-        <v>0</v>
+      <c r="BK203" t="inlineStr"/>
+      <c r="BL203" t="n">
+        <v>0.312958435207824</v>
       </c>
     </row>
     <row r="204">
@@ -22705,16 +23062,16 @@
           <t>Est</t>
         </is>
       </c>
-      <c r="AZ204" t="inlineStr">
-        <is>
-          <t>Kompienga</t>
-        </is>
+      <c r="AZ204" t="n">
+        <v>0</v>
       </c>
       <c r="BA204" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB204" t="n">
         <v>1</v>
+      </c>
+      <c r="BB204" t="inlineStr">
+        <is>
+          <t>BF52</t>
+        </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
@@ -22741,11 +23098,16 @@
       </c>
       <c r="BJ204" t="inlineStr">
         <is>
-          <t>27 July 2024</t>
-        </is>
-      </c>
-      <c r="BK204" t="n">
-        <v>0</v>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="BK204" t="inlineStr">
+        <is>
+          <t>Kompienga</t>
+        </is>
+      </c>
+      <c r="BL204" t="n">
+        <v>0.1942946872546454</v>
       </c>
     </row>
     <row r="205">
@@ -22849,7 +23211,8 @@
       <c r="BH205" t="inlineStr"/>
       <c r="BI205" t="inlineStr"/>
       <c r="BJ205" t="inlineStr"/>
-      <c r="BK205" t="n">
+      <c r="BK205" t="inlineStr"/>
+      <c r="BL205" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22954,8 +23317,9 @@
       <c r="BH206" t="inlineStr"/>
       <c r="BI206" t="inlineStr"/>
       <c r="BJ206" t="inlineStr"/>
-      <c r="BK206" t="n">
-        <v>0</v>
+      <c r="BK206" t="inlineStr"/>
+      <c r="BL206" t="n">
+        <v>0.1830350539860967</v>
       </c>
     </row>
     <row r="207">
@@ -23059,7 +23423,8 @@
       <c r="BH207" t="inlineStr"/>
       <c r="BI207" t="inlineStr"/>
       <c r="BJ207" t="inlineStr"/>
-      <c r="BK207" t="n">
+      <c r="BK207" t="inlineStr"/>
+      <c r="BL207" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23157,59 +23522,64 @@
           <t>Est</t>
         </is>
       </c>
-      <c r="AZ208" t="inlineStr">
+      <c r="AZ208" t="n">
+        <v>52</v>
+      </c>
+      <c r="BA208" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB208" t="inlineStr">
+        <is>
+          <t>BF52</t>
+        </is>
+      </c>
+      <c r="BC208" t="inlineStr">
+        <is>
+          <t>Protests ---- Battles</t>
+        </is>
+      </c>
+      <c r="BD208" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Non-state actor overtakes territory</t>
+        </is>
+      </c>
+      <c r="BE208" t="inlineStr">
+        <is>
+          <t>Protesters (Burkina Faso) ---- JNIM: Group for Support of Islam and Muslims</t>
+        </is>
+      </c>
+      <c r="BF208" t="inlineStr">
+        <is>
+          <t>Labor Group (Burkina Faso); Teachers (Burkina Faso)</t>
+        </is>
+      </c>
+      <c r="BG208" t="inlineStr">
+        <is>
+          <t>Military Forces of Burkina Faso (2022-)</t>
+        </is>
+      </c>
+      <c r="BH208" t="inlineStr">
+        <is>
+          <t>Military Forces of Burkina Faso (2022-) Gendarmerie; Police Forces of Burkina Faso (2022-) Prison Guards; VDP: Volunteer for Defense of Homeland</t>
+        </is>
+      </c>
+      <c r="BI208" t="inlineStr">
+        <is>
+          <t>On 26 April 2024, a number of teachers gathered and demonstrated peacefully in the town of Diapaga (Diapaga, Tapoa). The protesters called on the authorities to improve living and working conditions in the face of the humanitarian and food crisis. They also asked the authorities to take action on the case of community teachers who are still waiting to be paid. ---- On 13 May 2025, JNIM militants attacked the town of Diapaga (Tapoa, Est). They attacked the military camp, the gendarmerie post, the police station, the volunteer fighters (VDP), the civil prison, a school and the market. The militants took control of the village and the civil prison and freed around 30 prisoners. The militants set fire to the gendarmerie post, the police station, the health center, the local radio station, shops and a pharmacy. They also destroyed cell phone installations including the antenna. At least 52 people were killed, including soldiers, VDP, civilians and 2 nurses. JNIM claimed to have attacked and captured a military camp in Diapaga. In another statement, JNIM said its militants killed 160 soldiers in a raid on a military camp in the town of Diapaga, seized 1 military vehicle, one 14.5mm machine gun, one 12.7 machine gun, 3 mortars, 4 RPGs, 14 PKM rifles, 47 AK rifles, 6 pistols, 15 motorcycles, 405 magazines, 2 drones, and various other items. JNIM published photographs of the seizure. Fatalities coded as 52.</t>
+        </is>
+      </c>
+      <c r="BJ208" t="inlineStr">
+        <is>
+          <t>2024-04-26 ---- 2025-05-13</t>
+        </is>
+      </c>
+      <c r="BK208" t="inlineStr">
         <is>
           <t>Tapoa</t>
         </is>
       </c>
-      <c r="BA208" t="n">
-        <v>52</v>
-      </c>
-      <c r="BB208" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC208" t="inlineStr">
-        <is>
-          <t>Battles ---- Protests</t>
-        </is>
-      </c>
-      <c r="BD208" t="inlineStr">
-        <is>
-          <t>Non-state actor overtakes territory ---- Peaceful protest</t>
-        </is>
-      </c>
-      <c r="BE208" t="inlineStr">
-        <is>
-          <t>JNIM: Group for Support of Islam and Muslims ---- Protesters (Burkina Faso)</t>
-        </is>
-      </c>
-      <c r="BF208" t="inlineStr">
-        <is>
-          <t>Labor Group (Burkina Faso); Teachers (Burkina Faso)</t>
-        </is>
-      </c>
-      <c r="BG208" t="inlineStr">
-        <is>
-          <t>Military Forces of Burkina Faso (2022-)</t>
-        </is>
-      </c>
-      <c r="BH208" t="inlineStr">
-        <is>
-          <t>Police Forces of Burkina Faso (2022-) Gendarmerie; Police Forces of Burkina Faso (2022-) Prison Guards; VDP: Volunteer for Defense of Homeland</t>
-        </is>
-      </c>
-      <c r="BI208" t="inlineStr">
-        <is>
-          <t>On 13 May 2025, JNIM militants attacked the town of Diapaga (Tapoa, Est). They attacked the military camp, the gendarmerie post, the police station, the volunteer fighters (VDP), the civil prison, a school and the market. The militants took control of the village and the civil prison and freed around 30 prisoners. The militants set fire to the gendarmerie post, the police station, the health center, the local radio station, shops and a pharmacy. They also destroyed cell phone installations including the antenna. At least 52 people were killed, including soldiers, VDP, civilians and 2 nurses. JNIM claimed to have attacked and captured a military camp in Diapaga, without providing further details. 52 fatalities coded. ---- On 26 April 2024, a number of teachers gathered and demonstrated peacefully in the town of Diapaga (Diapaga, Tapoa). The protesters called on the authorities to improve living and working conditions in the face of the humanitarian and food crisis. They also asked the authorities to take action on the case of community teachers who are still waiting to be paid.</t>
-        </is>
-      </c>
-      <c r="BJ208" t="inlineStr">
-        <is>
-          <t>13 May 2025 ---- 26 April 2024</t>
-        </is>
-      </c>
-      <c r="BK208" t="n">
-        <v>0</v>
+      <c r="BL208" t="n">
+        <v>0.3282765281075208</v>
       </c>
     </row>
     <row r="209">
@@ -23313,8 +23683,9 @@
       <c r="BH209" t="inlineStr"/>
       <c r="BI209" t="inlineStr"/>
       <c r="BJ209" t="inlineStr"/>
-      <c r="BK209" t="n">
-        <v>0</v>
+      <c r="BK209" t="inlineStr"/>
+      <c r="BL209" t="n">
+        <v>0.02982991713911906</v>
       </c>
     </row>
     <row r="210">
@@ -23418,7 +23789,8 @@
       <c r="BH210" t="inlineStr"/>
       <c r="BI210" t="inlineStr"/>
       <c r="BJ210" t="inlineStr"/>
-      <c r="BK210" t="n">
+      <c r="BK210" t="inlineStr"/>
+      <c r="BL210" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23523,8 +23895,9 @@
       <c r="BH211" t="inlineStr"/>
       <c r="BI211" t="inlineStr"/>
       <c r="BJ211" t="inlineStr"/>
-      <c r="BK211" t="n">
-        <v>0</v>
+      <c r="BK211" t="inlineStr"/>
+      <c r="BL211" t="n">
+        <v>0.1305985425366413</v>
       </c>
     </row>
     <row r="212">
@@ -23628,8 +24001,9 @@
       <c r="BH212" t="inlineStr"/>
       <c r="BI212" t="inlineStr"/>
       <c r="BJ212" t="inlineStr"/>
-      <c r="BK212" t="n">
-        <v>0</v>
+      <c r="BK212" t="inlineStr"/>
+      <c r="BL212" t="n">
+        <v>0.0226800314102268</v>
       </c>
     </row>
     <row r="213">
@@ -23733,8 +24107,9 @@
       <c r="BH213" t="inlineStr"/>
       <c r="BI213" t="inlineStr"/>
       <c r="BJ213" t="inlineStr"/>
-      <c r="BK213" t="n">
-        <v>0</v>
+      <c r="BK213" t="inlineStr"/>
+      <c r="BL213" t="n">
+        <v>0.004279866021585412</v>
       </c>
     </row>
     <row r="214">
@@ -23838,8 +24213,9 @@
       <c r="BH214" t="inlineStr"/>
       <c r="BI214" t="inlineStr"/>
       <c r="BJ214" t="inlineStr"/>
-      <c r="BK214" t="n">
-        <v>0</v>
+      <c r="BK214" t="inlineStr"/>
+      <c r="BL214" t="n">
+        <v>0.02786469974668455</v>
       </c>
     </row>
     <row r="215">
@@ -23943,8 +24319,9 @@
       <c r="BH215" t="inlineStr"/>
       <c r="BI215" t="inlineStr"/>
       <c r="BJ215" t="inlineStr"/>
-      <c r="BK215" t="n">
-        <v>0</v>
+      <c r="BK215" t="inlineStr"/>
+      <c r="BL215" t="n">
+        <v>0.0500675397897457</v>
       </c>
     </row>
     <row r="216">
@@ -24041,16 +24418,16 @@
           <t>Hauts-Bassins</t>
         </is>
       </c>
-      <c r="AZ216" t="inlineStr">
-        <is>
-          <t>Houet</t>
-        </is>
+      <c r="AZ216" t="n">
+        <v>0</v>
       </c>
       <c r="BA216" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB216" t="n">
         <v>1</v>
+      </c>
+      <c r="BB216" t="inlineStr">
+        <is>
+          <t>BF53</t>
+        </is>
       </c>
       <c r="BC216" t="inlineStr">
         <is>
@@ -24081,11 +24458,16 @@
       </c>
       <c r="BJ216" t="inlineStr">
         <is>
-          <t>20 November 2024</t>
-        </is>
-      </c>
-      <c r="BK216" t="n">
-        <v>0</v>
+          <t>2024-11-20</t>
+        </is>
+      </c>
+      <c r="BK216" t="inlineStr">
+        <is>
+          <t>Houet</t>
+        </is>
+      </c>
+      <c r="BL216" t="n">
+        <v>0.02799015348971908</v>
       </c>
     </row>
     <row r="217">
@@ -24189,8 +24571,9 @@
       <c r="BH217" t="inlineStr"/>
       <c r="BI217" t="inlineStr"/>
       <c r="BJ217" t="inlineStr"/>
-      <c r="BK217" t="n">
-        <v>0</v>
+      <c r="BK217" t="inlineStr"/>
+      <c r="BL217" t="n">
+        <v>0.0768784113343398</v>
       </c>
     </row>
     <row r="218">
@@ -24294,8 +24677,9 @@
       <c r="BH218" t="inlineStr"/>
       <c r="BI218" t="inlineStr"/>
       <c r="BJ218" t="inlineStr"/>
-      <c r="BK218" t="n">
-        <v>0</v>
+      <c r="BK218" t="inlineStr"/>
+      <c r="BL218" t="n">
+        <v>0.006425478418773571</v>
       </c>
     </row>
     <row r="219">
@@ -24399,8 +24783,9 @@
       <c r="BH219" t="inlineStr"/>
       <c r="BI219" t="inlineStr"/>
       <c r="BJ219" t="inlineStr"/>
-      <c r="BK219" t="n">
-        <v>0</v>
+      <c r="BK219" t="inlineStr"/>
+      <c r="BL219" t="n">
+        <v>0.02797124241743429</v>
       </c>
     </row>
     <row r="220">
@@ -24504,8 +24889,9 @@
       <c r="BH220" t="inlineStr"/>
       <c r="BI220" t="inlineStr"/>
       <c r="BJ220" t="inlineStr"/>
-      <c r="BK220" t="n">
-        <v>0</v>
+      <c r="BK220" t="inlineStr"/>
+      <c r="BL220" t="n">
+        <v>0.01496955345060893</v>
       </c>
     </row>
     <row r="221">
@@ -24609,8 +24995,9 @@
       <c r="BH221" t="inlineStr"/>
       <c r="BI221" t="inlineStr"/>
       <c r="BJ221" t="inlineStr"/>
-      <c r="BK221" t="n">
-        <v>0</v>
+      <c r="BK221" t="inlineStr"/>
+      <c r="BL221" t="n">
+        <v>0.08992922143579372</v>
       </c>
     </row>
     <row r="222">
@@ -24714,8 +25101,9 @@
       <c r="BH222" t="inlineStr"/>
       <c r="BI222" t="inlineStr"/>
       <c r="BJ222" t="inlineStr"/>
-      <c r="BK222" t="n">
-        <v>0</v>
+      <c r="BK222" t="inlineStr"/>
+      <c r="BL222" t="n">
+        <v>0.08500661296140435</v>
       </c>
     </row>
     <row r="223">
@@ -24819,8 +25207,9 @@
       <c r="BH223" t="inlineStr"/>
       <c r="BI223" t="inlineStr"/>
       <c r="BJ223" t="inlineStr"/>
-      <c r="BK223" t="n">
-        <v>0</v>
+      <c r="BK223" t="inlineStr"/>
+      <c r="BL223" t="n">
+        <v>0.01978840125391849</v>
       </c>
     </row>
     <row r="224">
@@ -24924,8 +25313,9 @@
       <c r="BH224" t="inlineStr"/>
       <c r="BI224" t="inlineStr"/>
       <c r="BJ224" t="inlineStr"/>
-      <c r="BK224" t="n">
-        <v>0</v>
+      <c r="BK224" t="inlineStr"/>
+      <c r="BL224" t="n">
+        <v>0.05436709121635547</v>
       </c>
     </row>
     <row r="225">
@@ -25029,8 +25419,9 @@
       <c r="BH225" t="inlineStr"/>
       <c r="BI225" t="inlineStr"/>
       <c r="BJ225" t="inlineStr"/>
-      <c r="BK225" t="n">
-        <v>0</v>
+      <c r="BK225" t="inlineStr"/>
+      <c r="BL225" t="n">
+        <v>0.03546066586737988</v>
       </c>
     </row>
     <row r="226">
@@ -25134,8 +25525,9 @@
       <c r="BH226" t="inlineStr"/>
       <c r="BI226" t="inlineStr"/>
       <c r="BJ226" t="inlineStr"/>
-      <c r="BK226" t="n">
-        <v>0</v>
+      <c r="BK226" t="inlineStr"/>
+      <c r="BL226" t="n">
+        <v>0.1004985150615189</v>
       </c>
     </row>
     <row r="227">
@@ -25239,8 +25631,9 @@
       <c r="BH227" t="inlineStr"/>
       <c r="BI227" t="inlineStr"/>
       <c r="BJ227" t="inlineStr"/>
-      <c r="BK227" t="n">
-        <v>0</v>
+      <c r="BK227" t="inlineStr"/>
+      <c r="BL227" t="n">
+        <v>0.007488479262672811</v>
       </c>
     </row>
     <row r="228">
@@ -25344,8 +25737,9 @@
       <c r="BH228" t="inlineStr"/>
       <c r="BI228" t="inlineStr"/>
       <c r="BJ228" t="inlineStr"/>
-      <c r="BK228" t="n">
-        <v>0</v>
+      <c r="BK228" t="inlineStr"/>
+      <c r="BL228" t="n">
+        <v>0.08180737217598097</v>
       </c>
     </row>
     <row r="229">
@@ -25449,8 +25843,9 @@
       <c r="BH229" t="inlineStr"/>
       <c r="BI229" t="inlineStr"/>
       <c r="BJ229" t="inlineStr"/>
-      <c r="BK229" t="n">
-        <v>0</v>
+      <c r="BK229" t="inlineStr"/>
+      <c r="BL229" t="n">
+        <v>0.01694174226691442</v>
       </c>
     </row>
     <row r="230">
@@ -25554,8 +25949,9 @@
       <c r="BH230" t="inlineStr"/>
       <c r="BI230" t="inlineStr"/>
       <c r="BJ230" t="inlineStr"/>
-      <c r="BK230" t="n">
-        <v>0</v>
+      <c r="BK230" t="inlineStr"/>
+      <c r="BL230" t="n">
+        <v>0.0006684988486964273</v>
       </c>
     </row>
     <row r="231">
@@ -25659,8 +26055,9 @@
       <c r="BH231" t="inlineStr"/>
       <c r="BI231" t="inlineStr"/>
       <c r="BJ231" t="inlineStr"/>
-      <c r="BK231" t="n">
-        <v>0</v>
+      <c r="BK231" t="inlineStr"/>
+      <c r="BL231" t="n">
+        <v>0.02965471666942012</v>
       </c>
     </row>
     <row r="232">
@@ -25764,8 +26161,9 @@
       <c r="BH232" t="inlineStr"/>
       <c r="BI232" t="inlineStr"/>
       <c r="BJ232" t="inlineStr"/>
-      <c r="BK232" t="n">
-        <v>0</v>
+      <c r="BK232" t="inlineStr"/>
+      <c r="BL232" t="n">
+        <v>0.009046684304856192</v>
       </c>
     </row>
     <row r="233">
@@ -25869,8 +26267,9 @@
       <c r="BH233" t="inlineStr"/>
       <c r="BI233" t="inlineStr"/>
       <c r="BJ233" t="inlineStr"/>
-      <c r="BK233" t="n">
-        <v>0</v>
+      <c r="BK233" t="inlineStr"/>
+      <c r="BL233" t="n">
+        <v>0.019524267839956</v>
       </c>
     </row>
     <row r="234">
@@ -25974,8 +26373,9 @@
       <c r="BH234" t="inlineStr"/>
       <c r="BI234" t="inlineStr"/>
       <c r="BJ234" t="inlineStr"/>
-      <c r="BK234" t="n">
-        <v>0</v>
+      <c r="BK234" t="inlineStr"/>
+      <c r="BL234" t="n">
+        <v>0.01977949179009133</v>
       </c>
     </row>
     <row r="235">
@@ -26079,7 +26479,8 @@
       <c r="BH235" t="inlineStr"/>
       <c r="BI235" t="inlineStr"/>
       <c r="BJ235" t="inlineStr"/>
-      <c r="BK235" t="n">
+      <c r="BK235" t="inlineStr"/>
+      <c r="BL235" t="n">
         <v>0</v>
       </c>
     </row>
@@ -26184,8 +26585,9 @@
       <c r="BH236" t="inlineStr"/>
       <c r="BI236" t="inlineStr"/>
       <c r="BJ236" t="inlineStr"/>
-      <c r="BK236" t="n">
-        <v>0</v>
+      <c r="BK236" t="inlineStr"/>
+      <c r="BL236" t="n">
+        <v>0.003809757896030478</v>
       </c>
     </row>
     <row r="237">
@@ -26289,8 +26691,9 @@
       <c r="BH237" t="inlineStr"/>
       <c r="BI237" t="inlineStr"/>
       <c r="BJ237" t="inlineStr"/>
-      <c r="BK237" t="n">
-        <v>0</v>
+      <c r="BK237" t="inlineStr"/>
+      <c r="BL237" t="n">
+        <v>0.009629062260641207</v>
       </c>
     </row>
     <row r="238">
@@ -26394,8 +26797,9 @@
       <c r="BH238" t="inlineStr"/>
       <c r="BI238" t="inlineStr"/>
       <c r="BJ238" t="inlineStr"/>
-      <c r="BK238" t="n">
-        <v>0</v>
+      <c r="BK238" t="inlineStr"/>
+      <c r="BL238" t="n">
+        <v>0.002671848433325237</v>
       </c>
     </row>
     <row r="239">
@@ -26499,8 +26903,9 @@
       <c r="BH239" t="inlineStr"/>
       <c r="BI239" t="inlineStr"/>
       <c r="BJ239" t="inlineStr"/>
-      <c r="BK239" t="n">
-        <v>0</v>
+      <c r="BK239" t="inlineStr"/>
+      <c r="BL239" t="n">
+        <v>0.01568438520421819</v>
       </c>
     </row>
     <row r="240">
@@ -26604,8 +27009,9 @@
       <c r="BH240" t="inlineStr"/>
       <c r="BI240" t="inlineStr"/>
       <c r="BJ240" t="inlineStr"/>
-      <c r="BK240" t="n">
-        <v>0</v>
+      <c r="BK240" t="inlineStr"/>
+      <c r="BL240" t="n">
+        <v>0.004053323725454873</v>
       </c>
     </row>
     <row r="241">
@@ -26709,8 +27115,9 @@
       <c r="BH241" t="inlineStr"/>
       <c r="BI241" t="inlineStr"/>
       <c r="BJ241" t="inlineStr"/>
-      <c r="BK241" t="n">
-        <v>0</v>
+      <c r="BK241" t="inlineStr"/>
+      <c r="BL241" t="n">
+        <v>0.01097448102604786</v>
       </c>
     </row>
     <row r="242">
@@ -26807,16 +27214,16 @@
           <t>Hauts-Bassins</t>
         </is>
       </c>
-      <c r="AZ242" t="inlineStr">
-        <is>
-          <t>Tuy</t>
-        </is>
+      <c r="AZ242" t="n">
+        <v>0</v>
       </c>
       <c r="BA242" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB242" t="n">
         <v>1</v>
+      </c>
+      <c r="BB242" t="inlineStr">
+        <is>
+          <t>BF53</t>
+        </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
@@ -26847,11 +27254,16 @@
       </c>
       <c r="BJ242" t="inlineStr">
         <is>
-          <t>14 February 2024</t>
-        </is>
-      </c>
-      <c r="BK242" t="n">
-        <v>0</v>
+          <t>2024-02-14</t>
+        </is>
+      </c>
+      <c r="BK242" t="inlineStr">
+        <is>
+          <t>Tuy</t>
+        </is>
+      </c>
+      <c r="BL242" t="n">
+        <v>0.007985158896596225</v>
       </c>
     </row>
     <row r="243">
@@ -26955,8 +27367,9 @@
       <c r="BH243" t="inlineStr"/>
       <c r="BI243" t="inlineStr"/>
       <c r="BJ243" t="inlineStr"/>
-      <c r="BK243" t="n">
-        <v>0</v>
+      <c r="BK243" t="inlineStr"/>
+      <c r="BL243" t="n">
+        <v>0.008091908091908092</v>
       </c>
     </row>
     <row r="244">
@@ -27060,8 +27473,9 @@
       <c r="BH244" t="inlineStr"/>
       <c r="BI244" t="inlineStr"/>
       <c r="BJ244" t="inlineStr"/>
-      <c r="BK244" t="n">
-        <v>0</v>
+      <c r="BK244" t="inlineStr"/>
+      <c r="BL244" t="n">
+        <v>0.03917295333892148</v>
       </c>
     </row>
     <row r="245">
@@ -27165,8 +27579,9 @@
       <c r="BH245" t="inlineStr"/>
       <c r="BI245" t="inlineStr"/>
       <c r="BJ245" t="inlineStr"/>
-      <c r="BK245" t="n">
-        <v>0</v>
+      <c r="BK245" t="inlineStr"/>
+      <c r="BL245" t="n">
+        <v>0.1086750816803842</v>
       </c>
     </row>
     <row r="246">
@@ -27270,8 +27685,9 @@
       <c r="BH246" t="inlineStr"/>
       <c r="BI246" t="inlineStr"/>
       <c r="BJ246" t="inlineStr"/>
-      <c r="BK246" t="n">
-        <v>0</v>
+      <c r="BK246" t="inlineStr"/>
+      <c r="BL246" t="n">
+        <v>0.003478535852636572</v>
       </c>
     </row>
     <row r="247">
@@ -27375,8 +27791,9 @@
       <c r="BH247" t="inlineStr"/>
       <c r="BI247" t="inlineStr"/>
       <c r="BJ247" t="inlineStr"/>
-      <c r="BK247" t="n">
-        <v>0</v>
+      <c r="BK247" t="inlineStr"/>
+      <c r="BL247" t="n">
+        <v>0.1195979899497487</v>
       </c>
     </row>
     <row r="248">
@@ -27480,8 +27897,9 @@
       <c r="BH248" t="inlineStr"/>
       <c r="BI248" t="inlineStr"/>
       <c r="BJ248" t="inlineStr"/>
-      <c r="BK248" t="n">
-        <v>0</v>
+      <c r="BK248" t="inlineStr"/>
+      <c r="BL248" t="n">
+        <v>0.2479640910548253</v>
       </c>
     </row>
     <row r="249">
@@ -27585,7 +28003,8 @@
       <c r="BH249" t="inlineStr"/>
       <c r="BI249" t="inlineStr"/>
       <c r="BJ249" t="inlineStr"/>
-      <c r="BK249" t="n">
+      <c r="BK249" t="inlineStr"/>
+      <c r="BL249" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27690,8 +28109,9 @@
       <c r="BH250" t="inlineStr"/>
       <c r="BI250" t="inlineStr"/>
       <c r="BJ250" t="inlineStr"/>
-      <c r="BK250" t="n">
-        <v>0</v>
+      <c r="BK250" t="inlineStr"/>
+      <c r="BL250" t="n">
+        <v>0.1061446192146656</v>
       </c>
     </row>
     <row r="251">
@@ -27795,8 +28215,9 @@
       <c r="BH251" t="inlineStr"/>
       <c r="BI251" t="inlineStr"/>
       <c r="BJ251" t="inlineStr"/>
-      <c r="BK251" t="n">
-        <v>0</v>
+      <c r="BK251" t="inlineStr"/>
+      <c r="BL251" t="n">
+        <v>0.4876853040737715</v>
       </c>
     </row>
     <row r="252">
@@ -27900,8 +28321,9 @@
       <c r="BH252" t="inlineStr"/>
       <c r="BI252" t="inlineStr"/>
       <c r="BJ252" t="inlineStr"/>
-      <c r="BK252" t="n">
-        <v>0</v>
+      <c r="BK252" t="inlineStr"/>
+      <c r="BL252" t="n">
+        <v>0.01498778619633172</v>
       </c>
     </row>
     <row r="253">
@@ -28005,8 +28427,9 @@
       <c r="BH253" t="inlineStr"/>
       <c r="BI253" t="inlineStr"/>
       <c r="BJ253" t="inlineStr"/>
-      <c r="BK253" t="n">
-        <v>0</v>
+      <c r="BK253" t="inlineStr"/>
+      <c r="BL253" t="n">
+        <v>0.00453666517923546</v>
       </c>
     </row>
     <row r="254">
@@ -28110,8 +28533,9 @@
       <c r="BH254" t="inlineStr"/>
       <c r="BI254" t="inlineStr"/>
       <c r="BJ254" t="inlineStr"/>
-      <c r="BK254" t="n">
-        <v>0</v>
+      <c r="BK254" t="inlineStr"/>
+      <c r="BL254" t="n">
+        <v>0.00798537031392868</v>
       </c>
     </row>
     <row r="255">
@@ -28215,8 +28639,9 @@
       <c r="BH255" t="inlineStr"/>
       <c r="BI255" t="inlineStr"/>
       <c r="BJ255" t="inlineStr"/>
-      <c r="BK255" t="n">
-        <v>0</v>
+      <c r="BK255" t="inlineStr"/>
+      <c r="BL255" t="n">
+        <v>0.001536514822848879</v>
       </c>
     </row>
     <row r="256">
@@ -28320,8 +28745,9 @@
       <c r="BH256" t="inlineStr"/>
       <c r="BI256" t="inlineStr"/>
       <c r="BJ256" t="inlineStr"/>
-      <c r="BK256" t="n">
-        <v>0</v>
+      <c r="BK256" t="inlineStr"/>
+      <c r="BL256" t="n">
+        <v>0.005635413263639333</v>
       </c>
     </row>
     <row r="257">
@@ -28425,8 +28851,9 @@
       <c r="BH257" t="inlineStr"/>
       <c r="BI257" t="inlineStr"/>
       <c r="BJ257" t="inlineStr"/>
-      <c r="BK257" t="n">
-        <v>0</v>
+      <c r="BK257" t="inlineStr"/>
+      <c r="BL257" t="n">
+        <v>0.0001909125620465827</v>
       </c>
     </row>
     <row r="258">
@@ -28530,8 +28957,9 @@
       <c r="BH258" t="inlineStr"/>
       <c r="BI258" t="inlineStr"/>
       <c r="BJ258" t="inlineStr"/>
-      <c r="BK258" t="n">
-        <v>0</v>
+      <c r="BK258" t="inlineStr"/>
+      <c r="BL258" t="n">
+        <v>0.002782236490101658</v>
       </c>
     </row>
     <row r="259">
@@ -28635,7 +29063,8 @@
       <c r="BH259" t="inlineStr"/>
       <c r="BI259" t="inlineStr"/>
       <c r="BJ259" t="inlineStr"/>
-      <c r="BK259" t="n">
+      <c r="BK259" t="inlineStr"/>
+      <c r="BL259" t="n">
         <v>0</v>
       </c>
     </row>
@@ -28740,8 +29169,9 @@
       <c r="BH260" t="inlineStr"/>
       <c r="BI260" t="inlineStr"/>
       <c r="BJ260" t="inlineStr"/>
-      <c r="BK260" t="n">
-        <v>0</v>
+      <c r="BK260" t="inlineStr"/>
+      <c r="BL260" t="n">
+        <v>0.01615806526757163</v>
       </c>
     </row>
     <row r="261">
@@ -28845,7 +29275,8 @@
       <c r="BH261" t="inlineStr"/>
       <c r="BI261" t="inlineStr"/>
       <c r="BJ261" t="inlineStr"/>
-      <c r="BK261" t="n">
+      <c r="BK261" t="inlineStr"/>
+      <c r="BL261" t="n">
         <v>0</v>
       </c>
     </row>
@@ -28950,7 +29381,8 @@
       <c r="BH262" t="inlineStr"/>
       <c r="BI262" t="inlineStr"/>
       <c r="BJ262" t="inlineStr"/>
-      <c r="BK262" t="n">
+      <c r="BK262" t="inlineStr"/>
+      <c r="BL262" t="n">
         <v>0</v>
       </c>
     </row>
@@ -29055,8 +29487,9 @@
       <c r="BH263" t="inlineStr"/>
       <c r="BI263" t="inlineStr"/>
       <c r="BJ263" t="inlineStr"/>
-      <c r="BK263" t="n">
-        <v>0</v>
+      <c r="BK263" t="inlineStr"/>
+      <c r="BL263" t="n">
+        <v>0.03939843922782851</v>
       </c>
     </row>
     <row r="264">
@@ -29160,8 +29593,9 @@
       <c r="BH264" t="inlineStr"/>
       <c r="BI264" t="inlineStr"/>
       <c r="BJ264" t="inlineStr"/>
-      <c r="BK264" t="n">
-        <v>0</v>
+      <c r="BK264" t="inlineStr"/>
+      <c r="BL264" t="n">
+        <v>0.3371449314819857</v>
       </c>
     </row>
     <row r="265">
@@ -29265,7 +29699,8 @@
       <c r="BH265" t="inlineStr"/>
       <c r="BI265" t="inlineStr"/>
       <c r="BJ265" t="inlineStr"/>
-      <c r="BK265" t="n">
+      <c r="BK265" t="inlineStr"/>
+      <c r="BL265" t="n">
         <v>0</v>
       </c>
     </row>
@@ -29370,7 +29805,8 @@
       <c r="BH266" t="inlineStr"/>
       <c r="BI266" t="inlineStr"/>
       <c r="BJ266" t="inlineStr"/>
-      <c r="BK266" t="n">
+      <c r="BK266" t="inlineStr"/>
+      <c r="BL266" t="n">
         <v>0</v>
       </c>
     </row>
@@ -29475,8 +29911,9 @@
       <c r="BH267" t="inlineStr"/>
       <c r="BI267" t="inlineStr"/>
       <c r="BJ267" t="inlineStr"/>
-      <c r="BK267" t="n">
-        <v>0</v>
+      <c r="BK267" t="inlineStr"/>
+      <c r="BL267" t="n">
+        <v>0.4900013437412199</v>
       </c>
     </row>
     <row r="268">
@@ -29580,8 +30017,9 @@
       <c r="BH268" t="inlineStr"/>
       <c r="BI268" t="inlineStr"/>
       <c r="BJ268" t="inlineStr"/>
-      <c r="BK268" t="n">
-        <v>0</v>
+      <c r="BK268" t="inlineStr"/>
+      <c r="BL268" t="n">
+        <v>0.0345551812958193</v>
       </c>
     </row>
     <row r="269">
@@ -29685,8 +30123,9 @@
       <c r="BH269" t="inlineStr"/>
       <c r="BI269" t="inlineStr"/>
       <c r="BJ269" t="inlineStr"/>
-      <c r="BK269" t="n">
-        <v>0</v>
+      <c r="BK269" t="inlineStr"/>
+      <c r="BL269" t="n">
+        <v>0.1773357316686065</v>
       </c>
     </row>
     <row r="270">
@@ -29790,8 +30229,9 @@
       <c r="BH270" t="inlineStr"/>
       <c r="BI270" t="inlineStr"/>
       <c r="BJ270" t="inlineStr"/>
-      <c r="BK270" t="n">
-        <v>0</v>
+      <c r="BK270" t="inlineStr"/>
+      <c r="BL270" t="n">
+        <v>0.1748191099216969</v>
       </c>
     </row>
     <row r="271">
@@ -29888,16 +30328,16 @@
           <t>Nord</t>
         </is>
       </c>
-      <c r="AZ271" t="inlineStr">
-        <is>
-          <t>Yatenga</t>
-        </is>
+      <c r="AZ271" t="n">
+        <v>0</v>
       </c>
       <c r="BA271" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB271" t="n">
         <v>1</v>
+      </c>
+      <c r="BB271" t="inlineStr">
+        <is>
+          <t>BF54</t>
+        </is>
       </c>
       <c r="BC271" t="inlineStr">
         <is>
@@ -29928,10 +30368,15 @@
       </c>
       <c r="BJ271" t="inlineStr">
         <is>
-          <t>12 May 2025</t>
-        </is>
-      </c>
-      <c r="BK271" t="n">
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="BK271" t="inlineStr">
+        <is>
+          <t>Yatenga</t>
+        </is>
+      </c>
+      <c r="BL271" t="n">
         <v>0</v>
       </c>
     </row>
@@ -30036,7 +30481,8 @@
       <c r="BH272" t="inlineStr"/>
       <c r="BI272" t="inlineStr"/>
       <c r="BJ272" t="inlineStr"/>
-      <c r="BK272" t="n">
+      <c r="BK272" t="inlineStr"/>
+      <c r="BL272" t="n">
         <v>0</v>
       </c>
     </row>
@@ -30141,8 +30587,9 @@
       <c r="BH273" t="inlineStr"/>
       <c r="BI273" t="inlineStr"/>
       <c r="BJ273" t="inlineStr"/>
-      <c r="BK273" t="n">
-        <v>0</v>
+      <c r="BK273" t="inlineStr"/>
+      <c r="BL273" t="n">
+        <v>0.09061901723037652</v>
       </c>
     </row>
     <row r="274">
@@ -30246,7 +30693,8 @@
       <c r="BH274" t="inlineStr"/>
       <c r="BI274" t="inlineStr"/>
       <c r="BJ274" t="inlineStr"/>
-      <c r="BK274" t="n">
+      <c r="BK274" t="inlineStr"/>
+      <c r="BL274" t="n">
         <v>0</v>
       </c>
     </row>
@@ -30351,7 +30799,8 @@
       <c r="BH275" t="inlineStr"/>
       <c r="BI275" t="inlineStr"/>
       <c r="BJ275" t="inlineStr"/>
-      <c r="BK275" t="n">
+      <c r="BK275" t="inlineStr"/>
+      <c r="BL275" t="n">
         <v>0</v>
       </c>
     </row>
@@ -30449,16 +30898,16 @@
           <t>Nord</t>
         </is>
       </c>
-      <c r="AZ276" t="inlineStr">
-        <is>
-          <t>Zondoma</t>
-        </is>
+      <c r="AZ276" t="n">
+        <v>0</v>
       </c>
       <c r="BA276" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB276" t="n">
         <v>1</v>
+      </c>
+      <c r="BB276" t="inlineStr">
+        <is>
+          <t>BF54</t>
+        </is>
       </c>
       <c r="BC276" t="inlineStr">
         <is>
@@ -30485,10 +30934,15 @@
       </c>
       <c r="BJ276" t="inlineStr">
         <is>
-          <t>02 March 2024</t>
-        </is>
-      </c>
-      <c r="BK276" t="n">
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="BK276" t="inlineStr">
+        <is>
+          <t>Zondoma</t>
+        </is>
+      </c>
+      <c r="BL276" t="n">
         <v>0</v>
       </c>
     </row>
@@ -30593,7 +31047,8 @@
       <c r="BH277" t="inlineStr"/>
       <c r="BI277" t="inlineStr"/>
       <c r="BJ277" t="inlineStr"/>
-      <c r="BK277" t="n">
+      <c r="BK277" t="inlineStr"/>
+      <c r="BL277" t="n">
         <v>0</v>
       </c>
     </row>
@@ -30698,7 +31153,8 @@
       <c r="BH278" t="inlineStr"/>
       <c r="BI278" t="inlineStr"/>
       <c r="BJ278" t="inlineStr"/>
-      <c r="BK278" t="n">
+      <c r="BK278" t="inlineStr"/>
+      <c r="BL278" t="n">
         <v>0</v>
       </c>
     </row>
@@ -30803,8 +31259,9 @@
       <c r="BH279" t="inlineStr"/>
       <c r="BI279" t="inlineStr"/>
       <c r="BJ279" t="inlineStr"/>
-      <c r="BK279" t="n">
-        <v>0</v>
+      <c r="BK279" t="inlineStr"/>
+      <c r="BL279" t="n">
+        <v>0.01809457162851145</v>
       </c>
     </row>
     <row r="280">
@@ -30908,8 +31365,9 @@
       <c r="BH280" t="inlineStr"/>
       <c r="BI280" t="inlineStr"/>
       <c r="BJ280" t="inlineStr"/>
-      <c r="BK280" t="n">
-        <v>0</v>
+      <c r="BK280" t="inlineStr"/>
+      <c r="BL280" t="n">
+        <v>0.0104276385085317</v>
       </c>
     </row>
     <row r="281">
@@ -31013,8 +31471,9 @@
       <c r="BH281" t="inlineStr"/>
       <c r="BI281" t="inlineStr"/>
       <c r="BJ281" t="inlineStr"/>
-      <c r="BK281" t="n">
-        <v>0</v>
+      <c r="BK281" t="inlineStr"/>
+      <c r="BL281" t="n">
+        <v>0.02179755150791281</v>
       </c>
     </row>
     <row r="282">
@@ -31118,8 +31577,9 @@
       <c r="BH282" t="inlineStr"/>
       <c r="BI282" t="inlineStr"/>
       <c r="BJ282" t="inlineStr"/>
-      <c r="BK282" t="n">
-        <v>0</v>
+      <c r="BK282" t="inlineStr"/>
+      <c r="BL282" t="n">
+        <v>0.05779143536875496</v>
       </c>
     </row>
     <row r="283">
@@ -31223,8 +31683,9 @@
       <c r="BH283" t="inlineStr"/>
       <c r="BI283" t="inlineStr"/>
       <c r="BJ283" t="inlineStr"/>
-      <c r="BK283" t="n">
-        <v>0</v>
+      <c r="BK283" t="inlineStr"/>
+      <c r="BL283" t="n">
+        <v>0.0307852230929154</v>
       </c>
     </row>
     <row r="284">
@@ -31328,8 +31789,9 @@
       <c r="BH284" t="inlineStr"/>
       <c r="BI284" t="inlineStr"/>
       <c r="BJ284" t="inlineStr"/>
-      <c r="BK284" t="n">
-        <v>0</v>
+      <c r="BK284" t="inlineStr"/>
+      <c r="BL284" t="n">
+        <v>0.0207010115266996</v>
       </c>
     </row>
     <row r="285">
@@ -31433,8 +31895,9 @@
       <c r="BH285" t="inlineStr"/>
       <c r="BI285" t="inlineStr"/>
       <c r="BJ285" t="inlineStr"/>
-      <c r="BK285" t="n">
-        <v>0</v>
+      <c r="BK285" t="inlineStr"/>
+      <c r="BL285" t="n">
+        <v>0.03812808199310278</v>
       </c>
     </row>
     <row r="286">
@@ -31538,8 +32001,9 @@
       <c r="BH286" t="inlineStr"/>
       <c r="BI286" t="inlineStr"/>
       <c r="BJ286" t="inlineStr"/>
-      <c r="BK286" t="n">
-        <v>0</v>
+      <c r="BK286" t="inlineStr"/>
+      <c r="BL286" t="n">
+        <v>0.03361055348437052</v>
       </c>
     </row>
     <row r="287">
@@ -31643,8 +32107,9 @@
       <c r="BH287" t="inlineStr"/>
       <c r="BI287" t="inlineStr"/>
       <c r="BJ287" t="inlineStr"/>
-      <c r="BK287" t="n">
-        <v>0</v>
+      <c r="BK287" t="inlineStr"/>
+      <c r="BL287" t="n">
+        <v>0.02137185335360703</v>
       </c>
     </row>
     <row r="288">
@@ -31748,8 +32213,9 @@
       <c r="BH288" t="inlineStr"/>
       <c r="BI288" t="inlineStr"/>
       <c r="BJ288" t="inlineStr"/>
-      <c r="BK288" t="n">
-        <v>0</v>
+      <c r="BK288" t="inlineStr"/>
+      <c r="BL288" t="n">
+        <v>0.008076805851874428</v>
       </c>
     </row>
     <row r="289">
@@ -31853,8 +32319,9 @@
       <c r="BH289" t="inlineStr"/>
       <c r="BI289" t="inlineStr"/>
       <c r="BJ289" t="inlineStr"/>
-      <c r="BK289" t="n">
-        <v>0</v>
+      <c r="BK289" t="inlineStr"/>
+      <c r="BL289" t="n">
+        <v>0.02874551971326165</v>
       </c>
     </row>
     <row r="290">
@@ -31958,8 +32425,9 @@
       <c r="BH290" t="inlineStr"/>
       <c r="BI290" t="inlineStr"/>
       <c r="BJ290" t="inlineStr"/>
-      <c r="BK290" t="n">
-        <v>0</v>
+      <c r="BK290" t="inlineStr"/>
+      <c r="BL290" t="n">
+        <v>0.01255447188213322</v>
       </c>
     </row>
     <row r="291">
@@ -32063,8 +32531,9 @@
       <c r="BH291" t="inlineStr"/>
       <c r="BI291" t="inlineStr"/>
       <c r="BJ291" t="inlineStr"/>
-      <c r="BK291" t="n">
-        <v>0</v>
+      <c r="BK291" t="inlineStr"/>
+      <c r="BL291" t="n">
+        <v>0.01568671707482226</v>
       </c>
     </row>
     <row r="292">
@@ -32168,8 +32637,9 @@
       <c r="BH292" t="inlineStr"/>
       <c r="BI292" t="inlineStr"/>
       <c r="BJ292" t="inlineStr"/>
-      <c r="BK292" t="n">
-        <v>0</v>
+      <c r="BK292" t="inlineStr"/>
+      <c r="BL292" t="n">
+        <v>0.03125880033793298</v>
       </c>
     </row>
     <row r="293">
@@ -32273,8 +32743,9 @@
       <c r="BH293" t="inlineStr"/>
       <c r="BI293" t="inlineStr"/>
       <c r="BJ293" t="inlineStr"/>
-      <c r="BK293" t="n">
-        <v>0</v>
+      <c r="BK293" t="inlineStr"/>
+      <c r="BL293" t="n">
+        <v>0.1125091276751109</v>
       </c>
     </row>
     <row r="294">
@@ -32378,8 +32849,9 @@
       <c r="BH294" t="inlineStr"/>
       <c r="BI294" t="inlineStr"/>
       <c r="BJ294" t="inlineStr"/>
-      <c r="BK294" t="n">
-        <v>0</v>
+      <c r="BK294" t="inlineStr"/>
+      <c r="BL294" t="n">
+        <v>0.05656496400411382</v>
       </c>
     </row>
     <row r="295">
@@ -32483,8 +32955,9 @@
       <c r="BH295" t="inlineStr"/>
       <c r="BI295" t="inlineStr"/>
       <c r="BJ295" t="inlineStr"/>
-      <c r="BK295" t="n">
-        <v>0</v>
+      <c r="BK295" t="inlineStr"/>
+      <c r="BL295" t="n">
+        <v>0.3377620925887482</v>
       </c>
     </row>
     <row r="296">
@@ -32588,8 +33061,9 @@
       <c r="BH296" t="inlineStr"/>
       <c r="BI296" t="inlineStr"/>
       <c r="BJ296" t="inlineStr"/>
-      <c r="BK296" t="n">
-        <v>0</v>
+      <c r="BK296" t="inlineStr"/>
+      <c r="BL296" t="n">
+        <v>0.3090909090909091</v>
       </c>
     </row>
     <row r="297">
@@ -32693,8 +33167,9 @@
       <c r="BH297" t="inlineStr"/>
       <c r="BI297" t="inlineStr"/>
       <c r="BJ297" t="inlineStr"/>
-      <c r="BK297" t="n">
-        <v>0</v>
+      <c r="BK297" t="inlineStr"/>
+      <c r="BL297" t="n">
+        <v>0.02814053416463055</v>
       </c>
     </row>
     <row r="298">
@@ -32798,8 +33273,9 @@
       <c r="BH298" t="inlineStr"/>
       <c r="BI298" t="inlineStr"/>
       <c r="BJ298" t="inlineStr"/>
-      <c r="BK298" t="n">
-        <v>0</v>
+      <c r="BK298" t="inlineStr"/>
+      <c r="BL298" t="n">
+        <v>0.03337342152736019</v>
       </c>
     </row>
     <row r="299">
@@ -32903,7 +33379,8 @@
       <c r="BH299" t="inlineStr"/>
       <c r="BI299" t="inlineStr"/>
       <c r="BJ299" t="inlineStr"/>
-      <c r="BK299" t="n">
+      <c r="BK299" t="inlineStr"/>
+      <c r="BL299" t="n">
         <v>0</v>
       </c>
     </row>
@@ -33063,16 +33540,16 @@
           <t>Sahel</t>
         </is>
       </c>
-      <c r="AZ300" t="inlineStr">
-        <is>
-          <t>Oudalan</t>
-        </is>
+      <c r="AZ300" t="n">
+        <v>0</v>
       </c>
       <c r="BA300" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB300" t="n">
         <v>1</v>
+      </c>
+      <c r="BB300" t="inlineStr">
+        <is>
+          <t>BF56</t>
+        </is>
       </c>
       <c r="BC300" t="inlineStr">
         <is>
@@ -33107,11 +33584,16 @@
       </c>
       <c r="BJ300" t="inlineStr">
         <is>
-          <t>17 October 2024</t>
-        </is>
-      </c>
-      <c r="BK300" t="n">
-        <v>0</v>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="BK300" t="inlineStr">
+        <is>
+          <t>Oudalan</t>
+        </is>
+      </c>
+      <c r="BL300" t="n">
+        <v>0.4900146475652888</v>
       </c>
     </row>
     <row r="301">
@@ -33215,8 +33697,9 @@
       <c r="BH301" t="inlineStr"/>
       <c r="BI301" t="inlineStr"/>
       <c r="BJ301" t="inlineStr"/>
-      <c r="BK301" t="n">
-        <v>0</v>
+      <c r="BK301" t="inlineStr"/>
+      <c r="BL301" t="n">
+        <v>0.1590542718968297</v>
       </c>
     </row>
     <row r="302">
@@ -33320,8 +33803,9 @@
       <c r="BH302" t="inlineStr"/>
       <c r="BI302" t="inlineStr"/>
       <c r="BJ302" t="inlineStr"/>
-      <c r="BK302" t="n">
-        <v>0</v>
+      <c r="BK302" t="inlineStr"/>
+      <c r="BL302" t="n">
+        <v>0.3428103602262578</v>
       </c>
     </row>
     <row r="303">
@@ -33425,8 +33909,9 @@
       <c r="BH303" t="inlineStr"/>
       <c r="BI303" t="inlineStr"/>
       <c r="BJ303" t="inlineStr"/>
-      <c r="BK303" t="n">
-        <v>0</v>
+      <c r="BK303" t="inlineStr"/>
+      <c r="BL303" t="n">
+        <v>0.2051282051282051</v>
       </c>
     </row>
     <row r="304">
@@ -33530,8 +34015,9 @@
       <c r="BH304" t="inlineStr"/>
       <c r="BI304" t="inlineStr"/>
       <c r="BJ304" t="inlineStr"/>
-      <c r="BK304" t="n">
-        <v>0</v>
+      <c r="BK304" t="inlineStr"/>
+      <c r="BL304" t="n">
+        <v>0.04142686351377652</v>
       </c>
     </row>
     <row r="305">
@@ -33690,16 +34176,16 @@
           <t>Sahel</t>
         </is>
       </c>
-      <c r="AZ305" t="inlineStr">
-        <is>
-          <t>Seno</t>
-        </is>
+      <c r="AZ305" t="n">
+        <v>13</v>
       </c>
       <c r="BA305" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB305" t="n">
         <v>1</v>
+      </c>
+      <c r="BB305" t="inlineStr">
+        <is>
+          <t>BF56</t>
+        </is>
       </c>
       <c r="BC305" t="inlineStr">
         <is>
@@ -33734,11 +34220,16 @@
       </c>
       <c r="BJ305" t="inlineStr">
         <is>
-          <t>06 April 2024</t>
-        </is>
-      </c>
-      <c r="BK305" t="n">
-        <v>0</v>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="BK305" t="inlineStr">
+        <is>
+          <t>Seno</t>
+        </is>
+      </c>
+      <c r="BL305" t="n">
+        <v>0.4668379010785079</v>
       </c>
     </row>
     <row r="306">
@@ -33842,8 +34333,9 @@
       <c r="BH306" t="inlineStr"/>
       <c r="BI306" t="inlineStr"/>
       <c r="BJ306" t="inlineStr"/>
-      <c r="BK306" t="n">
-        <v>0</v>
+      <c r="BK306" t="inlineStr"/>
+      <c r="BL306" t="n">
+        <v>0.01715495940698906</v>
       </c>
     </row>
     <row r="307">
@@ -33947,8 +34439,9 @@
       <c r="BH307" t="inlineStr"/>
       <c r="BI307" t="inlineStr"/>
       <c r="BJ307" t="inlineStr"/>
-      <c r="BK307" t="n">
-        <v>0</v>
+      <c r="BK307" t="inlineStr"/>
+      <c r="BL307" t="n">
+        <v>0.9903520400648107</v>
       </c>
     </row>
     <row r="308">
@@ -34052,8 +34545,9 @@
       <c r="BH308" t="inlineStr"/>
       <c r="BI308" t="inlineStr"/>
       <c r="BJ308" t="inlineStr"/>
-      <c r="BK308" t="n">
-        <v>0</v>
+      <c r="BK308" t="inlineStr"/>
+      <c r="BL308" t="n">
+        <v>0.09958944281524927</v>
       </c>
     </row>
     <row r="309">
@@ -34157,8 +34651,9 @@
       <c r="BH309" t="inlineStr"/>
       <c r="BI309" t="inlineStr"/>
       <c r="BJ309" t="inlineStr"/>
-      <c r="BK309" t="n">
-        <v>0</v>
+      <c r="BK309" t="inlineStr"/>
+      <c r="BL309" t="n">
+        <v>0.2162817673731941</v>
       </c>
     </row>
     <row r="310">
@@ -34262,8 +34757,9 @@
       <c r="BH310" t="inlineStr"/>
       <c r="BI310" t="inlineStr"/>
       <c r="BJ310" t="inlineStr"/>
-      <c r="BK310" t="n">
-        <v>0</v>
+      <c r="BK310" t="inlineStr"/>
+      <c r="BL310" t="n">
+        <v>0.1414477898782832</v>
       </c>
     </row>
     <row r="311">
@@ -34367,7 +34863,8 @@
       <c r="BH311" t="inlineStr"/>
       <c r="BI311" t="inlineStr"/>
       <c r="BJ311" t="inlineStr"/>
-      <c r="BK311" t="n">
+      <c r="BK311" t="inlineStr"/>
+      <c r="BL311" t="n">
         <v>0</v>
       </c>
     </row>
@@ -34472,7 +34969,8 @@
       <c r="BH312" t="inlineStr"/>
       <c r="BI312" t="inlineStr"/>
       <c r="BJ312" t="inlineStr"/>
-      <c r="BK312" t="n">
+      <c r="BK312" t="inlineStr"/>
+      <c r="BL312" t="n">
         <v>0</v>
       </c>
     </row>
@@ -34577,8 +35075,9 @@
       <c r="BH313" t="inlineStr"/>
       <c r="BI313" t="inlineStr"/>
       <c r="BJ313" t="inlineStr"/>
-      <c r="BK313" t="n">
-        <v>0</v>
+      <c r="BK313" t="inlineStr"/>
+      <c r="BL313" t="n">
+        <v>0.4900061999940952</v>
       </c>
     </row>
     <row r="314">
@@ -34682,8 +35181,9 @@
       <c r="BH314" t="inlineStr"/>
       <c r="BI314" t="inlineStr"/>
       <c r="BJ314" t="inlineStr"/>
-      <c r="BK314" t="n">
-        <v>0</v>
+      <c r="BK314" t="inlineStr"/>
+      <c r="BL314" t="n">
+        <v>0.3483203755317588</v>
       </c>
     </row>
     <row r="315">
@@ -34787,7 +35287,8 @@
       <c r="BH315" t="inlineStr"/>
       <c r="BI315" t="inlineStr"/>
       <c r="BJ315" t="inlineStr"/>
-      <c r="BK315" t="n">
+      <c r="BK315" t="inlineStr"/>
+      <c r="BL315" t="n">
         <v>0</v>
       </c>
     </row>
@@ -34892,7 +35393,8 @@
       <c r="BH316" t="inlineStr"/>
       <c r="BI316" t="inlineStr"/>
       <c r="BJ316" t="inlineStr"/>
-      <c r="BK316" t="n">
+      <c r="BK316" t="inlineStr"/>
+      <c r="BL316" t="n">
         <v>0</v>
       </c>
     </row>
@@ -34997,7 +35499,8 @@
       <c r="BH317" t="inlineStr"/>
       <c r="BI317" t="inlineStr"/>
       <c r="BJ317" t="inlineStr"/>
-      <c r="BK317" t="n">
+      <c r="BK317" t="inlineStr"/>
+      <c r="BL317" t="n">
         <v>0</v>
       </c>
     </row>
@@ -35102,7 +35605,8 @@
       <c r="BH318" t="inlineStr"/>
       <c r="BI318" t="inlineStr"/>
       <c r="BJ318" t="inlineStr"/>
-      <c r="BK318" t="n">
+      <c r="BK318" t="inlineStr"/>
+      <c r="BL318" t="n">
         <v>0</v>
       </c>
     </row>
@@ -35207,8 +35711,9 @@
       <c r="BH319" t="inlineStr"/>
       <c r="BI319" t="inlineStr"/>
       <c r="BJ319" t="inlineStr"/>
-      <c r="BK319" t="n">
-        <v>0</v>
+      <c r="BK319" t="inlineStr"/>
+      <c r="BL319" t="n">
+        <v>0.001984455101703324</v>
       </c>
     </row>
     <row r="320">
@@ -35312,8 +35817,9 @@
       <c r="BH320" t="inlineStr"/>
       <c r="BI320" t="inlineStr"/>
       <c r="BJ320" t="inlineStr"/>
-      <c r="BK320" t="n">
-        <v>0</v>
+      <c r="BK320" t="inlineStr"/>
+      <c r="BL320" t="n">
+        <v>0.1355588737201365</v>
       </c>
     </row>
     <row r="321">
@@ -35410,30 +35916,30 @@
           <t>Sahel</t>
         </is>
       </c>
-      <c r="AZ321" t="inlineStr">
-        <is>
-          <t>Yagha</t>
-        </is>
+      <c r="AZ321" t="n">
+        <v>3</v>
       </c>
       <c r="BA321" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB321" t="n">
         <v>2</v>
       </c>
+      <c r="BB321" t="inlineStr">
+        <is>
+          <t>BF56</t>
+        </is>
+      </c>
       <c r="BC321" t="inlineStr">
         <is>
-          <t>Protests ---- Explosions/Remote violence</t>
+          <t>Explosions/Remote violence ---- Protests</t>
         </is>
       </c>
       <c r="BD321" t="inlineStr">
         <is>
-          <t>Peaceful protest ---- Air/drone strike</t>
+          <t>Air/drone strike ---- Peaceful protest</t>
         </is>
       </c>
       <c r="BE321" t="inlineStr">
         <is>
-          <t>Protesters (Burkina Faso) ---- Military Forces of Burkina Faso (2022-)</t>
+          <t>Military Forces of Burkina Faso (2022-) ---- Protesters (Burkina Faso)</t>
         </is>
       </c>
       <c r="BF321" t="inlineStr"/>
@@ -35445,16 +35951,21 @@
       <c r="BH321" t="inlineStr"/>
       <c r="BI321" t="inlineStr">
         <is>
-          <t>On 19 November 2024, hundreds of residents gathered and demonstrated peacefully in the town of Sebba (Sebba, Yagha). They demonstrated to claim security, the opening of schools, a food convoy, medical staff, pharmaceutical products, the opening of the hospital's operating theater, drinking water and the return of the police to the locality. ---- On 18 November 2024, the Burkinabe air force carried out airstrikes against JNIM militants hiding in an abandoned school and an orchard in Sebba (Sebba, Yagha). A number of militants were killed. Unknown fatalities coded to 3.</t>
+          <t>On 18 November 2024, the Burkinabe air force carried out airstrikes against JNIM militants hiding in an abandoned school and an orchard in Sebba (Sebba, Yagha). A number of militants were killed. Unknown fatalities coded to 3. ---- On 19 November 2024, hundreds of residents gathered and demonstrated peacefully in the town of Sebba (Sebba, Yagha). They demonstrated to claim security, the opening of schools, a food convoy, medical staff, pharmaceutical products, the opening of the hospital's operating theater, drinking water and the return of the police to the locality.</t>
         </is>
       </c>
       <c r="BJ321" t="inlineStr">
         <is>
-          <t>19 November 2024 ---- 18 November 2024</t>
-        </is>
-      </c>
-      <c r="BK321" t="n">
-        <v>0</v>
+          <t>2024-11-18 ---- 2024-11-19</t>
+        </is>
+      </c>
+      <c r="BK321" t="inlineStr">
+        <is>
+          <t>Yagha</t>
+        </is>
+      </c>
+      <c r="BL321" t="n">
+        <v>0.4415187663660169</v>
       </c>
     </row>
     <row r="322">
@@ -35558,8 +36069,9 @@
       <c r="BH322" t="inlineStr"/>
       <c r="BI322" t="inlineStr"/>
       <c r="BJ322" t="inlineStr"/>
-      <c r="BK322" t="n">
-        <v>0</v>
+      <c r="BK322" t="inlineStr"/>
+      <c r="BL322" t="n">
+        <v>0.1016648471615721</v>
       </c>
     </row>
     <row r="323">
@@ -35663,8 +36175,9 @@
       <c r="BH323" t="inlineStr"/>
       <c r="BI323" t="inlineStr"/>
       <c r="BJ323" t="inlineStr"/>
-      <c r="BK323" t="n">
-        <v>0</v>
+      <c r="BK323" t="inlineStr"/>
+      <c r="BL323" t="n">
+        <v>0.001342432039378006</v>
       </c>
     </row>
     <row r="324">
@@ -35768,8 +36281,9 @@
       <c r="BH324" t="inlineStr"/>
       <c r="BI324" t="inlineStr"/>
       <c r="BJ324" t="inlineStr"/>
-      <c r="BK324" t="n">
-        <v>0</v>
+      <c r="BK324" t="inlineStr"/>
+      <c r="BL324" t="n">
+        <v>0.02374114493586062</v>
       </c>
     </row>
     <row r="325">
@@ -35873,8 +36387,9 @@
       <c r="BH325" t="inlineStr"/>
       <c r="BI325" t="inlineStr"/>
       <c r="BJ325" t="inlineStr"/>
-      <c r="BK325" t="n">
-        <v>0</v>
+      <c r="BK325" t="inlineStr"/>
+      <c r="BL325" t="n">
+        <v>0.006366307541625857</v>
       </c>
     </row>
     <row r="326">
@@ -35978,8 +36493,9 @@
       <c r="BH326" t="inlineStr"/>
       <c r="BI326" t="inlineStr"/>
       <c r="BJ326" t="inlineStr"/>
-      <c r="BK326" t="n">
-        <v>0</v>
+      <c r="BK326" t="inlineStr"/>
+      <c r="BL326" t="n">
+        <v>0.1548519218651544</v>
       </c>
     </row>
     <row r="327">
@@ -36083,8 +36599,9 @@
       <c r="BH327" t="inlineStr"/>
       <c r="BI327" t="inlineStr"/>
       <c r="BJ327" t="inlineStr"/>
-      <c r="BK327" t="n">
-        <v>0</v>
+      <c r="BK327" t="inlineStr"/>
+      <c r="BL327" t="n">
+        <v>0.0320038213518032</v>
       </c>
     </row>
     <row r="328">
@@ -36188,8 +36705,9 @@
       <c r="BH328" t="inlineStr"/>
       <c r="BI328" t="inlineStr"/>
       <c r="BJ328" t="inlineStr"/>
-      <c r="BK328" t="n">
-        <v>0</v>
+      <c r="BK328" t="inlineStr"/>
+      <c r="BL328" t="n">
+        <v>0.03484230295965287</v>
       </c>
     </row>
     <row r="329">
@@ -36293,8 +36811,9 @@
       <c r="BH329" t="inlineStr"/>
       <c r="BI329" t="inlineStr"/>
       <c r="BJ329" t="inlineStr"/>
-      <c r="BK329" t="n">
-        <v>0</v>
+      <c r="BK329" t="inlineStr"/>
+      <c r="BL329" t="n">
+        <v>0.03281853281853282</v>
       </c>
     </row>
     <row r="330">
@@ -36398,8 +36917,9 @@
       <c r="BH330" t="inlineStr"/>
       <c r="BI330" t="inlineStr"/>
       <c r="BJ330" t="inlineStr"/>
-      <c r="BK330" t="n">
-        <v>0</v>
+      <c r="BK330" t="inlineStr"/>
+      <c r="BL330" t="n">
+        <v>0.01424172440338722</v>
       </c>
     </row>
     <row r="331">
@@ -36503,8 +37023,9 @@
       <c r="BH331" t="inlineStr"/>
       <c r="BI331" t="inlineStr"/>
       <c r="BJ331" t="inlineStr"/>
-      <c r="BK331" t="n">
-        <v>0</v>
+      <c r="BK331" t="inlineStr"/>
+      <c r="BL331" t="n">
+        <v>0.002333333333333334</v>
       </c>
     </row>
     <row r="332">
@@ -36608,8 +37129,9 @@
       <c r="BH332" t="inlineStr"/>
       <c r="BI332" t="inlineStr"/>
       <c r="BJ332" t="inlineStr"/>
-      <c r="BK332" t="n">
-        <v>0</v>
+      <c r="BK332" t="inlineStr"/>
+      <c r="BL332" t="n">
+        <v>0.005895549642614911</v>
       </c>
     </row>
     <row r="333">
@@ -36713,7 +37235,8 @@
       <c r="BH333" t="inlineStr"/>
       <c r="BI333" t="inlineStr"/>
       <c r="BJ333" t="inlineStr"/>
-      <c r="BK333" t="n">
+      <c r="BK333" t="inlineStr"/>
+      <c r="BL333" t="n">
         <v>0</v>
       </c>
     </row>
@@ -36818,8 +37341,9 @@
       <c r="BH334" t="inlineStr"/>
       <c r="BI334" t="inlineStr"/>
       <c r="BJ334" t="inlineStr"/>
-      <c r="BK334" t="n">
-        <v>0</v>
+      <c r="BK334" t="inlineStr"/>
+      <c r="BL334" t="n">
+        <v>0.03688608110862034</v>
       </c>
     </row>
     <row r="335">
@@ -36923,8 +37447,9 @@
       <c r="BH335" t="inlineStr"/>
       <c r="BI335" t="inlineStr"/>
       <c r="BJ335" t="inlineStr"/>
-      <c r="BK335" t="n">
-        <v>0</v>
+      <c r="BK335" t="inlineStr"/>
+      <c r="BL335" t="n">
+        <v>0.0188937128155652</v>
       </c>
     </row>
     <row r="336">
@@ -37028,8 +37553,9 @@
       <c r="BH336" t="inlineStr"/>
       <c r="BI336" t="inlineStr"/>
       <c r="BJ336" t="inlineStr"/>
-      <c r="BK336" t="n">
-        <v>0</v>
+      <c r="BK336" t="inlineStr"/>
+      <c r="BL336" t="n">
+        <v>0.01781059947871416</v>
       </c>
     </row>
     <row r="337">
@@ -37133,8 +37659,9 @@
       <c r="BH337" t="inlineStr"/>
       <c r="BI337" t="inlineStr"/>
       <c r="BJ337" t="inlineStr"/>
-      <c r="BK337" t="n">
-        <v>0</v>
+      <c r="BK337" t="inlineStr"/>
+      <c r="BL337" t="n">
+        <v>0.001615308151093439</v>
       </c>
     </row>
     <row r="338">
@@ -37238,8 +37765,9 @@
       <c r="BH338" t="inlineStr"/>
       <c r="BI338" t="inlineStr"/>
       <c r="BJ338" t="inlineStr"/>
-      <c r="BK338" t="n">
-        <v>0</v>
+      <c r="BK338" t="inlineStr"/>
+      <c r="BL338" t="n">
+        <v>0.1091099361092752</v>
       </c>
     </row>
     <row r="339">
@@ -37343,8 +37871,9 @@
       <c r="BH339" t="inlineStr"/>
       <c r="BI339" t="inlineStr"/>
       <c r="BJ339" t="inlineStr"/>
-      <c r="BK339" t="n">
-        <v>0</v>
+      <c r="BK339" t="inlineStr"/>
+      <c r="BL339" t="n">
+        <v>0.0737506966375627</v>
       </c>
     </row>
     <row r="340">
@@ -37448,8 +37977,9 @@
       <c r="BH340" t="inlineStr"/>
       <c r="BI340" t="inlineStr"/>
       <c r="BJ340" t="inlineStr"/>
-      <c r="BK340" t="n">
-        <v>0</v>
+      <c r="BK340" t="inlineStr"/>
+      <c r="BL340" t="n">
+        <v>0.02576808721506442</v>
       </c>
     </row>
     <row r="341">
@@ -37553,8 +38083,9 @@
       <c r="BH341" t="inlineStr"/>
       <c r="BI341" t="inlineStr"/>
       <c r="BJ341" t="inlineStr"/>
-      <c r="BK341" t="n">
-        <v>0</v>
+      <c r="BK341" t="inlineStr"/>
+      <c r="BL341" t="n">
+        <v>0.004065040650406504</v>
       </c>
     </row>
     <row r="342">
@@ -37658,8 +38189,9 @@
       <c r="BH342" t="inlineStr"/>
       <c r="BI342" t="inlineStr"/>
       <c r="BJ342" t="inlineStr"/>
-      <c r="BK342" t="n">
-        <v>0</v>
+      <c r="BK342" t="inlineStr"/>
+      <c r="BL342" t="n">
+        <v>0.1514226008680276</v>
       </c>
     </row>
     <row r="343">
@@ -37763,8 +38295,9 @@
       <c r="BH343" t="inlineStr"/>
       <c r="BI343" t="inlineStr"/>
       <c r="BJ343" t="inlineStr"/>
-      <c r="BK343" t="n">
-        <v>0</v>
+      <c r="BK343" t="inlineStr"/>
+      <c r="BL343" t="n">
+        <v>0.06864161849710983</v>
       </c>
     </row>
     <row r="344">
@@ -37868,7 +38401,8 @@
       <c r="BH344" t="inlineStr"/>
       <c r="BI344" t="inlineStr"/>
       <c r="BJ344" t="inlineStr"/>
-      <c r="BK344" t="n">
+      <c r="BK344" t="inlineStr"/>
+      <c r="BL344" t="n">
         <v>0</v>
       </c>
     </row>
@@ -37973,7 +38507,8 @@
       <c r="BH345" t="inlineStr"/>
       <c r="BI345" t="inlineStr"/>
       <c r="BJ345" t="inlineStr"/>
-      <c r="BK345" t="n">
+      <c r="BK345" t="inlineStr"/>
+      <c r="BL345" t="n">
         <v>0</v>
       </c>
     </row>
@@ -38078,8 +38613,9 @@
       <c r="BH346" t="inlineStr"/>
       <c r="BI346" t="inlineStr"/>
       <c r="BJ346" t="inlineStr"/>
-      <c r="BK346" t="n">
-        <v>0</v>
+      <c r="BK346" t="inlineStr"/>
+      <c r="BL346" t="n">
+        <v>0.1787238077178344</v>
       </c>
     </row>
     <row r="347">
@@ -38183,7 +38719,8 @@
       <c r="BH347" t="inlineStr"/>
       <c r="BI347" t="inlineStr"/>
       <c r="BJ347" t="inlineStr"/>
-      <c r="BK347" t="n">
+      <c r="BK347" t="inlineStr"/>
+      <c r="BL347" t="n">
         <v>0</v>
       </c>
     </row>
@@ -38288,8 +38825,9 @@
       <c r="BH348" t="inlineStr"/>
       <c r="BI348" t="inlineStr"/>
       <c r="BJ348" t="inlineStr"/>
-      <c r="BK348" t="n">
-        <v>0</v>
+      <c r="BK348" t="inlineStr"/>
+      <c r="BL348" t="n">
+        <v>0.6483711966793907</v>
       </c>
     </row>
     <row r="349">
@@ -38393,8 +38931,9 @@
       <c r="BH349" t="inlineStr"/>
       <c r="BI349" t="inlineStr"/>
       <c r="BJ349" t="inlineStr"/>
-      <c r="BK349" t="n">
-        <v>0</v>
+      <c r="BK349" t="inlineStr"/>
+      <c r="BL349" t="n">
+        <v>0.07640697766200963</v>
       </c>
     </row>
     <row r="350">
@@ -38498,7 +39037,8 @@
       <c r="BH350" t="inlineStr"/>
       <c r="BI350" t="inlineStr"/>
       <c r="BJ350" t="inlineStr"/>
-      <c r="BK350" t="n">
+      <c r="BK350" t="inlineStr"/>
+      <c r="BL350" t="n">
         <v>0</v>
       </c>
     </row>
@@ -38603,8 +39143,9 @@
       <c r="BH351" t="inlineStr"/>
       <c r="BI351" t="inlineStr"/>
       <c r="BJ351" t="inlineStr"/>
-      <c r="BK351" t="n">
-        <v>0</v>
+      <c r="BK351" t="inlineStr"/>
+      <c r="BL351" t="n">
+        <v>0.002259157656930773</v>
       </c>
     </row>
     <row r="352">
@@ -38708,8 +39249,9 @@
       <c r="BH352" t="inlineStr"/>
       <c r="BI352" t="inlineStr"/>
       <c r="BJ352" t="inlineStr"/>
-      <c r="BK352" t="n">
-        <v>0</v>
+      <c r="BK352" t="inlineStr"/>
+      <c r="BL352" t="n">
+        <v>0.03889457523029682</v>
       </c>
     </row>
   </sheetData>
@@ -38718,10 +39260,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C9824523CAB29F4DA646F20BAFE41B4C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9c972c102b01d47663811fb2ebdbd1e4">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5940141-1bc9-4c17-b1bc-e50f6b2083d6" xmlns:ns3="14cbb838-50ff-4dab-9c3f-cddf75f03c13" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bd0e8b72e466adcc572d3af37c1ebe05" ns2:_="" ns3:_="">
-    <xsd:import namespace="b5940141-1bc9-4c17-b1bc-e50f6b2083d6"/>
-    <xsd:import namespace="14cbb838-50ff-4dab-9c3f-cddf75f03c13"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DE51FB2AFBB2DD429D3D11FE759FFC43" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1354c8e90e28409d311bbba5db8dc335">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4877444-78fa-4cfa-bafc-d6c64fafc061" xmlns:ns3="d0fa6634-326e-4532-91a2-52bea7ac9212" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dbb4473bd7833dc3543803a005841490" ns2:_="" ns3:_="">
+    <xsd:import namespace="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
+    <xsd:import namespace="d0fa6634-326e-4532-91a2-52bea7ac9212"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -38733,13 +39275,15 @@
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
@@ -38748,7 +39292,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b5940141-1bc9-4c17-b1bc-e50f6b2083d6" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f4877444-78fa-4cfa-bafc-d6c64fafc061" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -38766,52 +39310,57 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="14" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="MediaServiceDateTaken" ma:index="13" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
         </xsd:sequence>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+    <xsd:element name="MediaServiceOCR" ma:index="20" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+    <xsd:element name="MediaServiceSearchProperties" ma:index="21" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="18" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="19" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="21" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="23" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="14cbb838-50ff-4dab-9c3f-cddf75f03c13" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d0fa6634-326e-4532-91a2-52bea7ac9212" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="SharedWithUsers" ma:index="11" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
@@ -38839,6 +39388,17 @@
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="19" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{d6bd4e25-e667-4943-8e38-5db701f530ee}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="d0fa6634-326e-4532-91a2-52bea7ac9212">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -38952,7 +39512,8 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5940141-1bc9-4c17-b1bc-e50f6b2083d6">
+    <TaxCatchAll xmlns="d0fa6634-326e-4532-91a2-52bea7ac9212" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4877444-78fa-4cfa-bafc-d6c64fafc061">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
@@ -38960,13 +39521,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E9532E7-10B3-4D67-9AD9-F2B98A9303B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB122704-8AD5-4AA5-AE7E-9ABC4B8F147B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E45674AB-3DCD-4B06-8814-542BC9AD6366}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CFEDC10-6B6B-4CFA-9187-F60CEAB532F3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FAF6BD4-4852-4B69-9438-04EBA0D727F3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FE3078D-3660-4F41-AA46-4D6D9FEF2596}"/>
 </file>